--- a/research/traditional_assets/database/data/malaysia/malaysia_green_renewable_energy.xlsx
+++ b/research/traditional_assets/database/data/malaysia/malaysia_green_renewable_energy.xlsx
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08008183558288937</v>
+        <v>0.07992383917749042</v>
       </c>
       <c r="C2">
-        <v>1172.894359994878</v>
+        <v>1165.575750117439</v>
       </c>
       <c r="D2">
-        <v>1027.494359994878</v>
+        <v>1032.251750117439</v>
       </c>
       <c r="E2">
-        <v>-240</v>
+        <v>-227.924</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>12.076</v>
       </c>
       <c r="G2">
         <v>145.4</v>
@@ -1457,28 +1457,28 @@
         <v>144.5</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.6074227999999999</v>
       </c>
       <c r="N2">
-        <v>144.5</v>
+        <v>143.8925772</v>
       </c>
       <c r="O2">
-        <v>34.68</v>
+        <v>34.534218528</v>
       </c>
       <c r="P2">
-        <v>109.82</v>
+        <v>109.358358672</v>
       </c>
       <c r="Q2">
-        <v>143.02</v>
+        <v>142.558358672</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08008183558288937</v>
+        <v>0.08034500927019235</v>
       </c>
       <c r="T2">
-        <v>0.5780409979533054</v>
+        <v>0.5824784844022399</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>237.8903129747517</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07992383917749042</v>
+        <v>0.07976584277209149</v>
       </c>
       <c r="C3">
-        <v>1165.575750117439</v>
+        <v>1158.301399441428</v>
       </c>
       <c r="D3">
-        <v>1032.251750117439</v>
+        <v>1037.053399441428</v>
       </c>
       <c r="E3">
-        <v>-227.924</v>
+        <v>-215.848</v>
       </c>
       <c r="F3">
-        <v>12.076</v>
+        <v>24.152</v>
       </c>
       <c r="G3">
         <v>145.4</v>
@@ -1539,28 +1539,28 @@
         <v>144.5</v>
       </c>
       <c r="M3">
-        <v>0.6074227999999999</v>
+        <v>1.2148456</v>
       </c>
       <c r="N3">
-        <v>143.8925772</v>
+        <v>143.2851544</v>
       </c>
       <c r="O3">
-        <v>34.534218528</v>
+        <v>34.388437056</v>
       </c>
       <c r="P3">
-        <v>109.358358672</v>
+        <v>108.896717344</v>
       </c>
       <c r="Q3">
-        <v>142.558358672</v>
+        <v>142.096717344</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08034500927019235</v>
+        <v>0.08061355384907296</v>
       </c>
       <c r="T3">
-        <v>0.5824784844022399</v>
+        <v>0.5870065317991118</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>237.8903129747517</v>
+        <v>118.9451564873759</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07976584277209149</v>
+        <v>0.07960784636669255</v>
       </c>
       <c r="C4">
-        <v>1158.301399441428</v>
+        <v>1151.07192848505</v>
       </c>
       <c r="D4">
-        <v>1037.053399441428</v>
+        <v>1041.89992848505</v>
       </c>
       <c r="E4">
-        <v>-215.848</v>
+        <v>-203.772</v>
       </c>
       <c r="F4">
-        <v>24.152</v>
+        <v>36.22799999999999</v>
       </c>
       <c r="G4">
         <v>145.4</v>
@@ -1621,28 +1621,28 @@
         <v>144.5</v>
       </c>
       <c r="M4">
-        <v>1.2148456</v>
+        <v>1.8222684</v>
       </c>
       <c r="N4">
-        <v>143.2851544</v>
+        <v>142.6777316</v>
       </c>
       <c r="O4">
-        <v>34.388437056</v>
+        <v>34.242655584</v>
       </c>
       <c r="P4">
-        <v>108.896717344</v>
+        <v>108.435076016</v>
       </c>
       <c r="Q4">
-        <v>142.096717344</v>
+        <v>141.635076016</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08061355384907296</v>
+        <v>0.08088763542957995</v>
       </c>
       <c r="T4">
-        <v>0.5870065317991118</v>
+        <v>0.5916279409979811</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>118.9451564873759</v>
+        <v>79.29677099158391</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07960784636669255</v>
+        <v>0.07944984996129362</v>
       </c>
       <c r="C5">
-        <v>1151.07192848505</v>
+        <v>1143.887969420608</v>
       </c>
       <c r="D5">
-        <v>1041.89992848505</v>
+        <v>1046.791969420608</v>
       </c>
       <c r="E5">
-        <v>-203.772</v>
+        <v>-191.696</v>
       </c>
       <c r="F5">
-        <v>36.22799999999999</v>
+        <v>48.30399999999999</v>
       </c>
       <c r="G5">
         <v>145.4</v>
@@ -1703,28 +1703,28 @@
         <v>144.5</v>
       </c>
       <c r="M5">
-        <v>1.8222684</v>
+        <v>2.4296912</v>
       </c>
       <c r="N5">
-        <v>142.6777316</v>
+        <v>142.0703088</v>
       </c>
       <c r="O5">
-        <v>34.242655584</v>
+        <v>34.09687411199999</v>
       </c>
       <c r="P5">
-        <v>108.435076016</v>
+        <v>107.973434688</v>
       </c>
       <c r="Q5">
-        <v>141.635076016</v>
+        <v>141.173434688</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08088763542957995</v>
+        <v>0.08116742704301419</v>
       </c>
       <c r="T5">
-        <v>0.5916279409979811</v>
+        <v>0.5963456295551601</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>79.29677099158391</v>
+        <v>59.47257824368793</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07944984996129362</v>
+        <v>0.07929185355589467</v>
       </c>
       <c r="C6">
-        <v>1143.887969420608</v>
+        <v>1136.75016634939</v>
       </c>
       <c r="D6">
-        <v>1046.791969420608</v>
+        <v>1051.73016634939</v>
       </c>
       <c r="E6">
-        <v>-191.696</v>
+        <v>-179.62</v>
       </c>
       <c r="F6">
-        <v>48.30399999999999</v>
+        <v>60.38</v>
       </c>
       <c r="G6">
         <v>145.4</v>
@@ -1785,28 +1785,28 @@
         <v>144.5</v>
       </c>
       <c r="M6">
-        <v>2.4296912</v>
+        <v>3.037113999999999</v>
       </c>
       <c r="N6">
-        <v>142.0703088</v>
+        <v>141.462886</v>
       </c>
       <c r="O6">
-        <v>34.09687411199999</v>
+        <v>33.95109264</v>
       </c>
       <c r="P6">
-        <v>107.973434688</v>
+        <v>107.51179336</v>
       </c>
       <c r="Q6">
-        <v>141.173434688</v>
+        <v>140.71179336</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08116742704301419</v>
+        <v>0.08145310900620494</v>
       </c>
       <c r="T6">
-        <v>0.5963456295551601</v>
+        <v>0.6011626378714376</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>59.47257824368793</v>
+        <v>47.57806259495035</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07929185355589467</v>
+        <v>0.07913385715049574</v>
       </c>
       <c r="C7">
-        <v>1136.75016634939</v>
+        <v>1129.659175584374</v>
       </c>
       <c r="D7">
-        <v>1051.73016634939</v>
+        <v>1056.715175584374</v>
       </c>
       <c r="E7">
-        <v>-179.62</v>
+        <v>-167.544</v>
       </c>
       <c r="F7">
-        <v>60.38</v>
+        <v>72.456</v>
       </c>
       <c r="G7">
         <v>145.4</v>
@@ -1867,28 +1867,28 @@
         <v>144.5</v>
       </c>
       <c r="M7">
-        <v>3.037113999999999</v>
+        <v>3.6445368</v>
       </c>
       <c r="N7">
-        <v>141.462886</v>
+        <v>140.8554632</v>
       </c>
       <c r="O7">
-        <v>33.95109264</v>
+        <v>33.805311168</v>
       </c>
       <c r="P7">
-        <v>107.51179336</v>
+        <v>107.050152032</v>
       </c>
       <c r="Q7">
-        <v>140.71179336</v>
+        <v>140.250152032</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08145310900620494</v>
+        <v>0.08174486930903803</v>
       </c>
       <c r="T7">
-        <v>0.6011626378714376</v>
+        <v>0.6060821357263594</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>47.57806259495035</v>
+        <v>39.64838549579195</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07913385715049574</v>
+        <v>0.07897586074509683</v>
       </c>
       <c r="C8">
-        <v>1129.659175584374</v>
+        <v>1122.61566594101</v>
       </c>
       <c r="D8">
-        <v>1056.715175584374</v>
+        <v>1061.74766594101</v>
       </c>
       <c r="E8">
-        <v>-167.544</v>
+        <v>-155.468</v>
       </c>
       <c r="F8">
-        <v>72.45599999999999</v>
+        <v>84.53199999999998</v>
       </c>
       <c r="G8">
         <v>145.4</v>
@@ -1949,28 +1949,28 @@
         <v>144.5</v>
       </c>
       <c r="M8">
-        <v>3.644536799999999</v>
+        <v>4.251959599999999</v>
       </c>
       <c r="N8">
-        <v>140.8554632</v>
+        <v>140.2480404</v>
       </c>
       <c r="O8">
-        <v>33.805311168</v>
+        <v>33.659529696</v>
       </c>
       <c r="P8">
-        <v>107.050152032</v>
+        <v>106.588510704</v>
       </c>
       <c r="Q8">
-        <v>140.250152032</v>
+        <v>139.788510704</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08174486930903803</v>
+        <v>0.08204290402698583</v>
       </c>
       <c r="T8">
-        <v>0.6060821357263594</v>
+        <v>0.6111074292340751</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>39.64838549579196</v>
+        <v>33.98433042496453</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07897586074509683</v>
+        <v>0.07881786433969788</v>
       </c>
       <c r="C9">
-        <v>1122.61566594101</v>
+        <v>1115.620319036362</v>
       </c>
       <c r="D9">
-        <v>1061.74766594101</v>
+        <v>1066.828319036362</v>
       </c>
       <c r="E9">
-        <v>-155.468</v>
+        <v>-143.392</v>
       </c>
       <c r="F9">
-        <v>84.532</v>
+        <v>96.60799999999999</v>
       </c>
       <c r="G9">
         <v>145.4</v>
@@ -2031,28 +2031,28 @@
         <v>144.5</v>
       </c>
       <c r="M9">
-        <v>4.251959599999999</v>
+        <v>4.859382399999999</v>
       </c>
       <c r="N9">
-        <v>140.2480404</v>
+        <v>139.6406176</v>
       </c>
       <c r="O9">
-        <v>33.659529696</v>
+        <v>33.513748224</v>
       </c>
       <c r="P9">
-        <v>106.588510704</v>
+        <v>106.126869376</v>
       </c>
       <c r="Q9">
-        <v>139.788510704</v>
+        <v>139.326869376</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08204290402698583</v>
+        <v>0.08234741776054116</v>
       </c>
       <c r="T9">
-        <v>0.6111074292340751</v>
+        <v>0.6162419682528282</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>33.98433042496453</v>
+        <v>29.73628912184397</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07881786433969788</v>
+        <v>0.07865986793429894</v>
       </c>
       <c r="C10">
-        <v>1115.620319036362</v>
+        <v>1108.67382959686</v>
       </c>
       <c r="D10">
-        <v>1066.828319036362</v>
+        <v>1071.957829596859</v>
       </c>
       <c r="E10">
-        <v>-143.392</v>
+        <v>-131.316</v>
       </c>
       <c r="F10">
-        <v>96.60799999999999</v>
+        <v>108.684</v>
       </c>
       <c r="G10">
         <v>145.4</v>
@@ -2113,28 +2113,28 @@
         <v>144.5</v>
       </c>
       <c r="M10">
-        <v>4.859382399999999</v>
+        <v>5.466805199999999</v>
       </c>
       <c r="N10">
-        <v>139.6406176</v>
+        <v>139.0331948</v>
       </c>
       <c r="O10">
-        <v>33.513748224</v>
+        <v>33.36796675199999</v>
       </c>
       <c r="P10">
-        <v>106.126869376</v>
+        <v>105.665228048</v>
       </c>
       <c r="Q10">
-        <v>139.326869376</v>
+        <v>138.865228048</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08234741776054116</v>
+        <v>0.08265862410362521</v>
       </c>
       <c r="T10">
-        <v>0.6162419682528282</v>
+        <v>0.6214893542829824</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>29.73628912184397</v>
+        <v>26.43225699719464</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07865986793429894</v>
+        <v>0.07850187152890002</v>
       </c>
       <c r="C11">
-        <v>1108.67382959686</v>
+        <v>1101.776905774988</v>
       </c>
       <c r="D11">
-        <v>1071.957829596859</v>
+        <v>1077.136905774988</v>
       </c>
       <c r="E11">
-        <v>-131.316</v>
+        <v>-119.24</v>
       </c>
       <c r="F11">
-        <v>108.684</v>
+        <v>120.76</v>
       </c>
       <c r="G11">
         <v>145.4</v>
@@ -2195,28 +2195,28 @@
         <v>144.5</v>
       </c>
       <c r="M11">
-        <v>5.466805199999999</v>
+        <v>6.074227999999999</v>
       </c>
       <c r="N11">
-        <v>139.0331948</v>
+        <v>138.425772</v>
       </c>
       <c r="O11">
-        <v>33.36796675199999</v>
+        <v>33.22218528</v>
       </c>
       <c r="P11">
-        <v>105.665228048</v>
+        <v>105.20358672</v>
       </c>
       <c r="Q11">
-        <v>138.865228048</v>
+        <v>138.40358672</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08265862410362521</v>
+        <v>0.08297674614322224</v>
       </c>
       <c r="T11">
-        <v>0.6214893542829824</v>
+        <v>0.6268533488915846</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>26.43225699719464</v>
+        <v>23.78903129747517</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07850187152890002</v>
+        <v>0.07834387512350109</v>
       </c>
       <c r="C12">
-        <v>1101.776905774988</v>
+        <v>1094.930269475197</v>
       </c>
       <c r="D12">
-        <v>1077.136905774988</v>
+        <v>1082.366269475197</v>
       </c>
       <c r="E12">
-        <v>-119.24</v>
+        <v>-107.164</v>
       </c>
       <c r="F12">
-        <v>120.76</v>
+        <v>132.836</v>
       </c>
       <c r="G12">
         <v>145.4</v>
@@ -2277,28 +2277,28 @@
         <v>144.5</v>
       </c>
       <c r="M12">
-        <v>6.074227999999999</v>
+        <v>6.681650799999999</v>
       </c>
       <c r="N12">
-        <v>138.425772</v>
+        <v>137.8183492</v>
       </c>
       <c r="O12">
-        <v>33.22218528</v>
+        <v>33.076403808</v>
       </c>
       <c r="P12">
-        <v>105.20358672</v>
+        <v>104.741945392</v>
       </c>
       <c r="Q12">
-        <v>138.40358672</v>
+        <v>137.941945392</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08297674614322224</v>
+        <v>0.08330201699269785</v>
       </c>
       <c r="T12">
-        <v>0.6268533488915846</v>
+        <v>0.6323378827048743</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>23.78903129747517</v>
+        <v>21.62639208861379</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07834387512350109</v>
+        <v>0.07818587871810213</v>
       </c>
       <c r="C13">
-        <v>1094.930269475197</v>
+        <v>1088.134656689349</v>
       </c>
       <c r="D13">
-        <v>1082.366269475197</v>
+        <v>1087.646656689349</v>
       </c>
       <c r="E13">
-        <v>-107.164</v>
+        <v>-95.08800000000002</v>
       </c>
       <c r="F13">
-        <v>132.836</v>
+        <v>144.912</v>
       </c>
       <c r="G13">
         <v>145.4</v>
@@ -2359,28 +2359,28 @@
         <v>144.5</v>
       </c>
       <c r="M13">
-        <v>6.681650799999999</v>
+        <v>7.289073599999998</v>
       </c>
       <c r="N13">
-        <v>137.8183492</v>
+        <v>137.2109264</v>
       </c>
       <c r="O13">
-        <v>33.076403808</v>
+        <v>32.930622336</v>
       </c>
       <c r="P13">
-        <v>104.741945392</v>
+        <v>104.280304064</v>
       </c>
       <c r="Q13">
-        <v>137.941945392</v>
+        <v>137.480304064</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08330201699269785</v>
+        <v>0.0836346803614797</v>
       </c>
       <c r="T13">
-        <v>0.6323378827048743</v>
+        <v>0.6379470650139206</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>21.62639208861379</v>
+        <v>19.82419274789598</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07818587871810213</v>
+        <v>0.0780278823127032</v>
       </c>
       <c r="C14">
-        <v>1088.134656689349</v>
+        <v>1081.390817842034</v>
       </c>
       <c r="D14">
-        <v>1087.646656689349</v>
+        <v>1092.978817842034</v>
       </c>
       <c r="E14">
-        <v>-95.08800000000002</v>
+        <v>-83.012</v>
       </c>
       <c r="F14">
-        <v>144.912</v>
+        <v>156.988</v>
       </c>
       <c r="G14">
         <v>145.4</v>
@@ -2441,28 +2441,28 @@
         <v>144.5</v>
       </c>
       <c r="M14">
-        <v>7.289073599999998</v>
+        <v>7.896496399999999</v>
       </c>
       <c r="N14">
-        <v>137.2109264</v>
+        <v>136.6035036</v>
       </c>
       <c r="O14">
-        <v>32.930622336</v>
+        <v>32.784840864</v>
       </c>
       <c r="P14">
-        <v>104.280304064</v>
+        <v>103.818662736</v>
       </c>
       <c r="Q14">
-        <v>137.480304064</v>
+        <v>137.018662736</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.0836346803614797</v>
+        <v>0.08397499116402668</v>
       </c>
       <c r="T14">
-        <v>0.6379470650139206</v>
+        <v>0.6436851940427153</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>19.82419274789598</v>
+        <v>18.29925484421167</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.0780278823127032</v>
+        <v>0.07786988590730427</v>
       </c>
       <c r="C15">
-        <v>1081.390817842034</v>
+        <v>1074.699518146093</v>
       </c>
       <c r="D15">
-        <v>1092.978817842034</v>
+        <v>1098.363518146093</v>
       </c>
       <c r="E15">
-        <v>-83.012</v>
+        <v>-70.93600000000001</v>
       </c>
       <c r="F15">
-        <v>156.988</v>
+        <v>169.064</v>
       </c>
       <c r="G15">
         <v>145.4</v>
@@ -2523,28 +2523,28 @@
         <v>144.5</v>
       </c>
       <c r="M15">
-        <v>7.896496399999999</v>
+        <v>8.503919199999999</v>
       </c>
       <c r="N15">
-        <v>136.6035036</v>
+        <v>135.9960808</v>
       </c>
       <c r="O15">
-        <v>32.784840864</v>
+        <v>32.639059392</v>
       </c>
       <c r="P15">
-        <v>103.818662736</v>
+        <v>103.357021408</v>
       </c>
       <c r="Q15">
-        <v>137.018662736</v>
+        <v>136.557021408</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08397499116402668</v>
+        <v>0.08432321617128405</v>
       </c>
       <c r="T15">
-        <v>0.6436851940427153</v>
+        <v>0.6495567679326446</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>18.29925484421167</v>
+        <v>16.99216521248227</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07786988590730427</v>
+        <v>0.07771188950190534</v>
       </c>
       <c r="C16">
-        <v>1074.699518146093</v>
+        <v>1068.061537968706</v>
       </c>
       <c r="D16">
-        <v>1098.363518146093</v>
+        <v>1103.801537968706</v>
       </c>
       <c r="E16">
-        <v>-70.93600000000001</v>
+        <v>-58.85999999999999</v>
       </c>
       <c r="F16">
-        <v>169.064</v>
+        <v>181.14</v>
       </c>
       <c r="G16">
         <v>145.4</v>
@@ -2605,28 +2605,28 @@
         <v>144.5</v>
       </c>
       <c r="M16">
-        <v>8.503919199999999</v>
+        <v>9.111342</v>
       </c>
       <c r="N16">
-        <v>135.9960808</v>
+        <v>135.388658</v>
       </c>
       <c r="O16">
-        <v>32.639059392</v>
+        <v>32.49327792</v>
       </c>
       <c r="P16">
-        <v>103.357021408</v>
+        <v>102.89538008</v>
       </c>
       <c r="Q16">
-        <v>136.557021408</v>
+        <v>136.09538008</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08432321617128405</v>
+        <v>0.08467963470812394</v>
       </c>
       <c r="T16">
-        <v>0.6495567679326446</v>
+        <v>0.6555664965023371</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>16.99216521248227</v>
+        <v>15.85935419831678</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07771188950190533</v>
+        <v>0.0775538930965064</v>
       </c>
       <c r="C17">
-        <v>1068.061537968707</v>
+        <v>1061.477673208403</v>
       </c>
       <c r="D17">
-        <v>1103.801537968707</v>
+        <v>1109.293673208403</v>
       </c>
       <c r="E17">
-        <v>-58.86000000000001</v>
+        <v>-46.78400000000002</v>
       </c>
       <c r="F17">
-        <v>181.14</v>
+        <v>193.216</v>
       </c>
       <c r="G17">
         <v>145.4</v>
@@ -2687,28 +2687,28 @@
         <v>144.5</v>
       </c>
       <c r="M17">
-        <v>9.111341999999999</v>
+        <v>9.718764799999999</v>
       </c>
       <c r="N17">
-        <v>135.388658</v>
+        <v>134.7812352</v>
       </c>
       <c r="O17">
-        <v>32.49327792</v>
+        <v>32.347496448</v>
       </c>
       <c r="P17">
-        <v>102.89538008</v>
+        <v>102.433738752</v>
       </c>
       <c r="Q17">
-        <v>136.09538008</v>
+        <v>135.633738752</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08467963470812392</v>
+        <v>0.08504453940060286</v>
       </c>
       <c r="T17">
-        <v>0.6555664965023369</v>
+        <v>0.6617193138474983</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>15.85935419831678</v>
+        <v>14.86814456092198</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.0775538930965064</v>
+        <v>0.07739589669110747</v>
       </c>
       <c r="C18">
-        <v>1061.477673208403</v>
+        <v>1054.948735683387</v>
       </c>
       <c r="D18">
-        <v>1109.293673208403</v>
+        <v>1114.840735683387</v>
       </c>
       <c r="E18">
-        <v>-46.78400000000002</v>
+        <v>-34.708</v>
       </c>
       <c r="F18">
-        <v>193.216</v>
+        <v>205.292</v>
       </c>
       <c r="G18">
         <v>145.4</v>
@@ -2769,28 +2769,28 @@
         <v>144.5</v>
       </c>
       <c r="M18">
-        <v>9.718764799999999</v>
+        <v>10.3261876</v>
       </c>
       <c r="N18">
-        <v>134.7812352</v>
+        <v>134.1738124</v>
       </c>
       <c r="O18">
-        <v>32.347496448</v>
+        <v>32.201714976</v>
       </c>
       <c r="P18">
-        <v>102.433738752</v>
+        <v>101.972097424</v>
       </c>
       <c r="Q18">
-        <v>135.633738752</v>
+        <v>135.172097424</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08504453940060286</v>
+        <v>0.08541823697723791</v>
       </c>
       <c r="T18">
-        <v>0.6617193138474983</v>
+        <v>0.668020391851579</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>14.86814456092198</v>
+        <v>13.99354782204422</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07739589669110747</v>
+        <v>0.07723790028570854</v>
       </c>
       <c r="C19">
-        <v>1054.948735683387</v>
+        <v>1048.475553531573</v>
       </c>
       <c r="D19">
-        <v>1114.840735683387</v>
+        <v>1120.443553531573</v>
       </c>
       <c r="E19">
-        <v>-34.708</v>
+        <v>-22.63200000000001</v>
       </c>
       <c r="F19">
-        <v>205.292</v>
+        <v>217.368</v>
       </c>
       <c r="G19">
         <v>145.4</v>
@@ -2851,28 +2851,28 @@
         <v>144.5</v>
       </c>
       <c r="M19">
-        <v>10.3261876</v>
+        <v>10.9336104</v>
       </c>
       <c r="N19">
-        <v>134.1738124</v>
+        <v>133.5663896</v>
       </c>
       <c r="O19">
-        <v>32.201714976</v>
+        <v>32.055933504</v>
       </c>
       <c r="P19">
-        <v>101.972097424</v>
+        <v>101.510456096</v>
       </c>
       <c r="Q19">
-        <v>135.172097424</v>
+        <v>134.710456096</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08541823697723791</v>
+        <v>0.08580104912891286</v>
       </c>
       <c r="T19">
-        <v>0.668020391851579</v>
+        <v>0.6744751546850277</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>13.99354782204422</v>
+        <v>13.21612849859732</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07723790028570854</v>
+        <v>0.07729650388030961</v>
       </c>
       <c r="C20">
-        <v>1048.475553531573</v>
+        <v>1034.31481358602</v>
       </c>
       <c r="D20">
-        <v>1120.443553531573</v>
+        <v>1118.35881358602</v>
       </c>
       <c r="E20">
-        <v>-22.63200000000003</v>
+        <v>-10.55600000000001</v>
       </c>
       <c r="F20">
-        <v>217.368</v>
+        <v>229.444</v>
       </c>
       <c r="G20">
         <v>145.4</v>
@@ -2933,45 +2933,45 @@
         <v>144.5</v>
       </c>
       <c r="M20">
-        <v>10.9336104</v>
+        <v>11.8851992</v>
       </c>
       <c r="N20">
-        <v>133.5663896</v>
+        <v>132.6148008</v>
       </c>
       <c r="O20">
-        <v>32.055933504</v>
+        <v>31.827552192</v>
       </c>
       <c r="P20">
-        <v>101.510456096</v>
+        <v>100.787248608</v>
       </c>
       <c r="Q20">
-        <v>134.710456096</v>
+        <v>133.987248608</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08580104912891284</v>
+        <v>0.08619331343248099</v>
       </c>
       <c r="T20">
-        <v>0.6744751546850276</v>
+        <v>0.6810892943785614</v>
       </c>
       <c r="U20">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V20">
         <v>0.24</v>
       </c>
       <c r="W20">
-        <v>0.038228</v>
+        <v>0.039368</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y20">
-        <v>13.21612849859732</v>
+        <v>12.15797880779314</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07729650388030961</v>
+        <v>0.07714990747491067</v>
       </c>
       <c r="C21">
-        <v>1034.31481358602</v>
+        <v>1027.468410584006</v>
       </c>
       <c r="D21">
-        <v>1118.35881358602</v>
+        <v>1123.588410584006</v>
       </c>
       <c r="E21">
-        <v>-10.55600000000001</v>
+        <v>1.519999999999982</v>
       </c>
       <c r="F21">
-        <v>229.444</v>
+        <v>241.52</v>
       </c>
       <c r="G21">
         <v>145.4</v>
@@ -3015,28 +3015,28 @@
         <v>144.5</v>
       </c>
       <c r="M21">
-        <v>11.8851992</v>
+        <v>12.510736</v>
       </c>
       <c r="N21">
-        <v>132.6148008</v>
+        <v>131.989264</v>
       </c>
       <c r="O21">
-        <v>31.827552192</v>
+        <v>31.67742336</v>
       </c>
       <c r="P21">
-        <v>100.787248608</v>
+        <v>100.31184064</v>
       </c>
       <c r="Q21">
-        <v>133.987248608</v>
+        <v>133.51184064</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08619331343248099</v>
+        <v>0.08659538434363834</v>
       </c>
       <c r="T21">
-        <v>0.6810892943785614</v>
+        <v>0.6878687875644335</v>
       </c>
       <c r="U21">
         <v>0.0518</v>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>12.15797880779314</v>
+        <v>11.55007986740348</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07714990747491067</v>
+        <v>0.07700331106951173</v>
       </c>
       <c r="C22">
-        <v>1027.468410584006</v>
+        <v>1020.671145964767</v>
       </c>
       <c r="D22">
-        <v>1123.588410584006</v>
+        <v>1128.867145964767</v>
       </c>
       <c r="E22">
-        <v>1.519999999999982</v>
+        <v>13.596</v>
       </c>
       <c r="F22">
-        <v>241.52</v>
+        <v>253.596</v>
       </c>
       <c r="G22">
         <v>145.4</v>
@@ -3097,28 +3097,28 @@
         <v>144.5</v>
       </c>
       <c r="M22">
-        <v>12.510736</v>
+        <v>13.1362728</v>
       </c>
       <c r="N22">
-        <v>131.989264</v>
+        <v>131.3637272</v>
       </c>
       <c r="O22">
-        <v>31.67742336</v>
+        <v>31.527294528</v>
       </c>
       <c r="P22">
-        <v>100.31184064</v>
+        <v>99.836432672</v>
       </c>
       <c r="Q22">
-        <v>133.51184064</v>
+        <v>133.036432672</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08659538434363834</v>
+        <v>0.08700763426520472</v>
       </c>
       <c r="T22">
-        <v>0.6878687875644335</v>
+        <v>0.6948199134891884</v>
       </c>
       <c r="U22">
         <v>0.0518</v>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>11.55007986740348</v>
+        <v>11.0000760641938</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07700331106951173</v>
+        <v>0.0768567146641128</v>
       </c>
       <c r="C23">
-        <v>1020.671145964767</v>
+        <v>1013.923715569157</v>
       </c>
       <c r="D23">
-        <v>1128.867145964767</v>
+        <v>1134.195715569157</v>
       </c>
       <c r="E23">
-        <v>13.59599999999998</v>
+        <v>25.67199999999997</v>
       </c>
       <c r="F23">
-        <v>253.596</v>
+        <v>265.672</v>
       </c>
       <c r="G23">
         <v>145.4</v>
@@ -3179,28 +3179,28 @@
         <v>144.5</v>
       </c>
       <c r="M23">
-        <v>13.1362728</v>
+        <v>13.7618096</v>
       </c>
       <c r="N23">
-        <v>131.3637272</v>
+        <v>130.7381904</v>
       </c>
       <c r="O23">
-        <v>31.527294528</v>
+        <v>31.377165696</v>
       </c>
       <c r="P23">
-        <v>99.836432672</v>
+        <v>99.361024704</v>
       </c>
       <c r="Q23">
-        <v>133.036432672</v>
+        <v>132.561024704</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.08700763426520472</v>
+        <v>0.08743045469758051</v>
       </c>
       <c r="T23">
-        <v>0.6948199134891884</v>
+        <v>0.7019492734120141</v>
       </c>
       <c r="U23">
         <v>0.0518</v>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>11.0000760641938</v>
+        <v>10.50007260673044</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.0768567146641128</v>
+        <v>0.07671011825871388</v>
       </c>
       <c r="C24">
-        <v>1013.923715569157</v>
+        <v>1007.226828438594</v>
       </c>
       <c r="D24">
-        <v>1134.195715569157</v>
+        <v>1139.574828438594</v>
       </c>
       <c r="E24">
-        <v>25.67199999999997</v>
+        <v>37.74799999999999</v>
       </c>
       <c r="F24">
-        <v>265.672</v>
+        <v>277.748</v>
       </c>
       <c r="G24">
         <v>145.4</v>
@@ -3261,28 +3261,28 @@
         <v>144.5</v>
       </c>
       <c r="M24">
-        <v>13.7618096</v>
+        <v>14.3873464</v>
       </c>
       <c r="N24">
-        <v>130.7381904</v>
+        <v>130.1126536</v>
       </c>
       <c r="O24">
-        <v>31.377165696</v>
+        <v>31.227036864</v>
       </c>
       <c r="P24">
-        <v>99.361024704</v>
+        <v>98.88561673599999</v>
       </c>
       <c r="Q24">
-        <v>132.561024704</v>
+        <v>132.085616736</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.08743045469758051</v>
+        <v>0.08786425747884918</v>
       </c>
       <c r="T24">
-        <v>0.7019492734120141</v>
+        <v>0.7092638115146532</v>
       </c>
       <c r="U24">
         <v>0.0518</v>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>10.50007260673044</v>
+        <v>10.04354771078564</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07671011825871388</v>
+        <v>0.07687360185331493</v>
       </c>
       <c r="C25">
-        <v>1007.226828438594</v>
+        <v>989.1553281374233</v>
       </c>
       <c r="D25">
-        <v>1139.574828438594</v>
+        <v>1133.579328137423</v>
       </c>
       <c r="E25">
-        <v>37.74799999999999</v>
+        <v>49.82400000000001</v>
       </c>
       <c r="F25">
-        <v>277.748</v>
+        <v>289.824</v>
       </c>
       <c r="G25">
         <v>145.4</v>
@@ -3343,45 +3343,45 @@
         <v>144.5</v>
       </c>
       <c r="M25">
-        <v>14.3873464</v>
+        <v>15.505584</v>
       </c>
       <c r="N25">
-        <v>130.1126536</v>
+        <v>128.994416</v>
       </c>
       <c r="O25">
-        <v>31.227036864</v>
+        <v>30.95865984</v>
       </c>
       <c r="P25">
-        <v>98.88561673599999</v>
+        <v>98.03575616000001</v>
       </c>
       <c r="Q25">
-        <v>132.085616736</v>
+        <v>131.23575616</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.08786425747884918</v>
+        <v>0.08830947612278281</v>
       </c>
       <c r="T25">
-        <v>0.7092638115146532</v>
+        <v>0.7167708374620987</v>
       </c>
       <c r="U25">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V25">
         <v>0.24</v>
       </c>
       <c r="W25">
-        <v>0.039368</v>
+        <v>0.04066</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y25">
-        <v>10.04354771078564</v>
+        <v>9.319223319805303</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07687360185331493</v>
+        <v>0.076739925447916</v>
       </c>
       <c r="C26">
-        <v>989.1553281374235</v>
+        <v>981.9769743866053</v>
       </c>
       <c r="D26">
-        <v>1133.579328137423</v>
+        <v>1138.476974386605</v>
       </c>
       <c r="E26">
-        <v>49.82399999999996</v>
+        <v>61.89999999999998</v>
       </c>
       <c r="F26">
-        <v>289.824</v>
+        <v>301.9</v>
       </c>
       <c r="G26">
         <v>145.4</v>
@@ -3425,28 +3425,28 @@
         <v>144.5</v>
       </c>
       <c r="M26">
-        <v>15.505584</v>
+        <v>16.15165</v>
       </c>
       <c r="N26">
-        <v>128.994416</v>
+        <v>128.34835</v>
       </c>
       <c r="O26">
-        <v>30.95865984</v>
+        <v>30.803604</v>
       </c>
       <c r="P26">
-        <v>98.03575616000001</v>
+        <v>97.544746</v>
       </c>
       <c r="Q26">
-        <v>131.23575616</v>
+        <v>130.744746</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.08830947612278281</v>
+        <v>0.088766567263888</v>
       </c>
       <c r="T26">
-        <v>0.7167708374620987</v>
+        <v>0.7244780507681429</v>
       </c>
       <c r="U26">
         <v>0.0535</v>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>9.319223319805305</v>
+        <v>8.946454387013091</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.076739925447916</v>
+        <v>0.07660624904251706</v>
       </c>
       <c r="C27">
-        <v>981.9769743866053</v>
+        <v>974.8411249825255</v>
       </c>
       <c r="D27">
-        <v>1138.476974386605</v>
+        <v>1143.417124982525</v>
       </c>
       <c r="E27">
-        <v>61.89999999999998</v>
+        <v>73.976</v>
       </c>
       <c r="F27">
-        <v>301.9</v>
+        <v>313.976</v>
       </c>
       <c r="G27">
         <v>145.4</v>
@@ -3507,28 +3507,28 @@
         <v>144.5</v>
       </c>
       <c r="M27">
-        <v>16.15165</v>
+        <v>16.797716</v>
       </c>
       <c r="N27">
-        <v>128.34835</v>
+        <v>127.702284</v>
       </c>
       <c r="O27">
-        <v>30.803604</v>
+        <v>30.64854816</v>
       </c>
       <c r="P27">
-        <v>97.544746</v>
+        <v>97.05373584</v>
       </c>
       <c r="Q27">
-        <v>130.744746</v>
+        <v>130.25373584</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.088766567263888</v>
+        <v>0.08923601221961765</v>
       </c>
       <c r="T27">
-        <v>0.7244780507681429</v>
+        <v>0.7323935671365124</v>
       </c>
       <c r="U27">
         <v>0.0535</v>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>8.946454387013091</v>
+        <v>8.602359987512587</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07660624904251706</v>
+        <v>0.07647257263711812</v>
       </c>
       <c r="C28">
-        <v>974.8411249825255</v>
+        <v>967.7483356491874</v>
       </c>
       <c r="D28">
-        <v>1143.417124982525</v>
+        <v>1148.400335649187</v>
       </c>
       <c r="E28">
-        <v>73.976</v>
+        <v>86.05200000000002</v>
       </c>
       <c r="F28">
-        <v>313.976</v>
+        <v>326.052</v>
       </c>
       <c r="G28">
         <v>145.4</v>
@@ -3589,28 +3589,28 @@
         <v>144.5</v>
       </c>
       <c r="M28">
-        <v>16.797716</v>
+        <v>17.443782</v>
       </c>
       <c r="N28">
-        <v>127.702284</v>
+        <v>127.056218</v>
       </c>
       <c r="O28">
-        <v>30.64854816</v>
+        <v>30.49349232</v>
       </c>
       <c r="P28">
-        <v>97.05373584</v>
+        <v>96.56272568</v>
       </c>
       <c r="Q28">
-        <v>130.25373584</v>
+        <v>129.76272568</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.08923601221961765</v>
+        <v>0.08971831868098373</v>
       </c>
       <c r="T28">
-        <v>0.7323935671365124</v>
+        <v>0.7405259469670291</v>
       </c>
       <c r="U28">
         <v>0.0535</v>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>8.602359987512587</v>
+        <v>8.283754062049159</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07647257263711812</v>
+        <v>0.07633889623171919</v>
       </c>
       <c r="C29">
-        <v>967.7483356491874</v>
+        <v>960.6991718407676</v>
       </c>
       <c r="D29">
-        <v>1148.400335649187</v>
+        <v>1153.427171840767</v>
       </c>
       <c r="E29">
-        <v>86.05200000000002</v>
+        <v>98.12799999999999</v>
       </c>
       <c r="F29">
-        <v>326.052</v>
+        <v>338.128</v>
       </c>
       <c r="G29">
         <v>145.4</v>
@@ -3671,28 +3671,28 @@
         <v>144.5</v>
       </c>
       <c r="M29">
-        <v>17.443782</v>
+        <v>18.089848</v>
       </c>
       <c r="N29">
-        <v>127.056218</v>
+        <v>126.410152</v>
       </c>
       <c r="O29">
-        <v>30.49349232</v>
+        <v>30.33843648</v>
       </c>
       <c r="P29">
-        <v>96.56272568</v>
+        <v>96.07171552</v>
       </c>
       <c r="Q29">
-        <v>129.76272568</v>
+        <v>129.27171552</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.08971831868098373</v>
+        <v>0.09021402254405443</v>
       </c>
       <c r="T29">
-        <v>0.7405259469670291</v>
+        <v>0.7488842262372823</v>
       </c>
       <c r="U29">
         <v>0.0535</v>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>8.283754062049159</v>
+        <v>7.98790570269026</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07633889623171919</v>
+        <v>0.07620521982632027</v>
       </c>
       <c r="C30">
-        <v>960.6991718407676</v>
+        <v>953.694208955508</v>
       </c>
       <c r="D30">
-        <v>1153.427171840767</v>
+        <v>1158.498208955508</v>
       </c>
       <c r="E30">
-        <v>98.12799999999999</v>
+        <v>110.204</v>
       </c>
       <c r="F30">
-        <v>338.128</v>
+        <v>350.204</v>
       </c>
       <c r="G30">
         <v>145.4</v>
@@ -3753,28 +3753,28 @@
         <v>144.5</v>
       </c>
       <c r="M30">
-        <v>18.089848</v>
+        <v>18.735914</v>
       </c>
       <c r="N30">
-        <v>126.410152</v>
+        <v>125.764086</v>
       </c>
       <c r="O30">
-        <v>30.33843648</v>
+        <v>30.18338064</v>
       </c>
       <c r="P30">
-        <v>96.07171552</v>
+        <v>95.58070536</v>
       </c>
       <c r="Q30">
-        <v>129.27171552</v>
+        <v>128.78070536</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09021402254405443</v>
+        <v>0.09072368989622573</v>
       </c>
       <c r="T30">
-        <v>0.7488842262372823</v>
+        <v>0.7574779499940217</v>
       </c>
       <c r="U30">
         <v>0.0535</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>7.98790570269026</v>
+        <v>7.712460678459561</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07620521982632025</v>
+        <v>0.07625394342092132</v>
       </c>
       <c r="C31">
-        <v>953.6942089555087</v>
+        <v>939.7647150976186</v>
       </c>
       <c r="D31">
-        <v>1158.498208955509</v>
+        <v>1156.644715097618</v>
       </c>
       <c r="E31">
-        <v>110.204</v>
+        <v>122.28</v>
       </c>
       <c r="F31">
-        <v>350.204</v>
+        <v>362.28</v>
       </c>
       <c r="G31">
         <v>145.4</v>
@@ -3835,45 +3835,45 @@
         <v>144.5</v>
       </c>
       <c r="M31">
-        <v>18.735914</v>
+        <v>19.671804</v>
       </c>
       <c r="N31">
-        <v>125.764086</v>
+        <v>124.828196</v>
       </c>
       <c r="O31">
-        <v>30.18338064</v>
+        <v>29.95876704</v>
       </c>
       <c r="P31">
-        <v>95.58070536000001</v>
+        <v>94.86942896000001</v>
       </c>
       <c r="Q31">
-        <v>128.78070536</v>
+        <v>128.06942896</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09072368989622573</v>
+        <v>0.09124791917274475</v>
       </c>
       <c r="T31">
-        <v>0.7574779499940217</v>
+        <v>0.7663172087152391</v>
       </c>
       <c r="U31">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V31">
         <v>0.24</v>
       </c>
       <c r="W31">
-        <v>0.04066</v>
+        <v>0.041268</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y31">
-        <v>7.712460678459563</v>
+        <v>7.345538822977294</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07625394342092132</v>
+        <v>0.07612634701552239</v>
       </c>
       <c r="C32">
-        <v>939.7647150976186</v>
+        <v>932.5552329111417</v>
       </c>
       <c r="D32">
-        <v>1156.644715097618</v>
+        <v>1161.511232911142</v>
       </c>
       <c r="E32">
-        <v>122.28</v>
+        <v>134.356</v>
       </c>
       <c r="F32">
-        <v>362.28</v>
+        <v>374.356</v>
       </c>
       <c r="G32">
         <v>145.4</v>
@@ -3917,28 +3917,28 @@
         <v>144.5</v>
       </c>
       <c r="M32">
-        <v>19.671804</v>
+        <v>20.3275308</v>
       </c>
       <c r="N32">
-        <v>124.828196</v>
+        <v>124.1724692</v>
       </c>
       <c r="O32">
-        <v>29.95876704</v>
+        <v>29.801392608</v>
       </c>
       <c r="P32">
-        <v>94.86942896000001</v>
+        <v>94.37107659199999</v>
       </c>
       <c r="Q32">
-        <v>128.06942896</v>
+        <v>127.571076592</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09124791917274475</v>
+        <v>0.0917873435007571</v>
       </c>
       <c r="T32">
-        <v>0.7663172087152391</v>
+        <v>0.7754126778341732</v>
       </c>
       <c r="U32">
         <v>0.0543</v>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>7.345538822977294</v>
+        <v>7.10858595771996</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07612634701552239</v>
+        <v>0.07599875061012344</v>
       </c>
       <c r="C33">
-        <v>932.5552329111417</v>
+        <v>925.3868749544613</v>
       </c>
       <c r="D33">
-        <v>1161.511232911142</v>
+        <v>1166.418874954461</v>
       </c>
       <c r="E33">
-        <v>134.356</v>
+        <v>146.432</v>
       </c>
       <c r="F33">
-        <v>374.356</v>
+        <v>386.432</v>
       </c>
       <c r="G33">
         <v>145.4</v>
@@ -3999,28 +3999,28 @@
         <v>144.5</v>
       </c>
       <c r="M33">
-        <v>20.3275308</v>
+        <v>20.9832576</v>
       </c>
       <c r="N33">
-        <v>124.1724692</v>
+        <v>123.5167424</v>
       </c>
       <c r="O33">
-        <v>29.801392608</v>
+        <v>29.644018176</v>
       </c>
       <c r="P33">
-        <v>94.37107659199999</v>
+        <v>93.872724224</v>
       </c>
       <c r="Q33">
-        <v>127.571076592</v>
+        <v>127.072724224</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.0917873435007571</v>
+        <v>0.09234263325018155</v>
       </c>
       <c r="T33">
-        <v>0.7754126778341732</v>
+        <v>0.7847756607507229</v>
       </c>
       <c r="U33">
         <v>0.0543</v>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>7.10858595771996</v>
+        <v>6.886442646541212</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07599875061012344</v>
+        <v>0.07587115420472451</v>
       </c>
       <c r="C34">
-        <v>925.3868749544613</v>
+        <v>918.260164716351</v>
       </c>
       <c r="D34">
-        <v>1166.418874954461</v>
+        <v>1171.368164716351</v>
       </c>
       <c r="E34">
-        <v>146.432</v>
+        <v>158.508</v>
       </c>
       <c r="F34">
-        <v>386.432</v>
+        <v>398.508</v>
       </c>
       <c r="G34">
         <v>145.4</v>
@@ -4081,28 +4081,28 @@
         <v>144.5</v>
       </c>
       <c r="M34">
-        <v>20.9832576</v>
+        <v>21.6389844</v>
       </c>
       <c r="N34">
-        <v>123.5167424</v>
+        <v>122.8610156</v>
       </c>
       <c r="O34">
-        <v>29.644018176</v>
+        <v>29.486643744</v>
       </c>
       <c r="P34">
-        <v>93.872724224</v>
+        <v>93.37437185600001</v>
       </c>
       <c r="Q34">
-        <v>127.072724224</v>
+        <v>126.574371856</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.09234263325018155</v>
+        <v>0.09291449881302166</v>
       </c>
       <c r="T34">
-        <v>0.7847756607507229</v>
+        <v>0.7944181356946323</v>
       </c>
       <c r="U34">
         <v>0.0543</v>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>6.886442646541212</v>
+        <v>6.677762566342994</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07587115420472451</v>
+        <v>0.07574355779932559</v>
       </c>
       <c r="C35">
-        <v>918.260164716351</v>
+        <v>911.1756346084123</v>
       </c>
       <c r="D35">
-        <v>1171.368164716351</v>
+        <v>1176.359634608412</v>
       </c>
       <c r="E35">
-        <v>158.508</v>
+        <v>170.584</v>
       </c>
       <c r="F35">
-        <v>398.508</v>
+        <v>410.584</v>
       </c>
       <c r="G35">
         <v>145.4</v>
@@ -4163,28 +4163,28 @@
         <v>144.5</v>
       </c>
       <c r="M35">
-        <v>21.6389844</v>
+        <v>22.2947112</v>
       </c>
       <c r="N35">
-        <v>122.8610156</v>
+        <v>122.2052888</v>
       </c>
       <c r="O35">
-        <v>29.486643744</v>
+        <v>29.329269312</v>
       </c>
       <c r="P35">
-        <v>93.37437185600001</v>
+        <v>92.876019488</v>
       </c>
       <c r="Q35">
-        <v>126.574371856</v>
+        <v>126.076019488</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.09291449881302166</v>
+        <v>0.09350369363534181</v>
       </c>
       <c r="T35">
-        <v>0.7944181356946323</v>
+        <v>0.8043528068489633</v>
       </c>
       <c r="U35">
         <v>0.0543</v>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>6.677762566342994</v>
+        <v>6.481357784979964</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07574355779932559</v>
+        <v>0.07561596139392665</v>
       </c>
       <c r="C36">
-        <v>911.1756346084123</v>
+        <v>904.1338261559981</v>
       </c>
       <c r="D36">
-        <v>1176.359634608412</v>
+        <v>1181.393826155998</v>
       </c>
       <c r="E36">
-        <v>170.584</v>
+        <v>182.66</v>
       </c>
       <c r="F36">
-        <v>410.584</v>
+        <v>422.66</v>
       </c>
       <c r="G36">
         <v>145.4</v>
@@ -4245,28 +4245,28 @@
         <v>144.5</v>
       </c>
       <c r="M36">
-        <v>22.2947112</v>
+        <v>22.950438</v>
       </c>
       <c r="N36">
-        <v>122.2052888</v>
+        <v>121.549562</v>
       </c>
       <c r="O36">
-        <v>29.329269312</v>
+        <v>29.17189488</v>
       </c>
       <c r="P36">
-        <v>92.876019488</v>
+        <v>92.37766712</v>
       </c>
       <c r="Q36">
-        <v>126.076019488</v>
+        <v>125.57766712</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.09350369363534181</v>
+        <v>0.09411101752911794</v>
       </c>
       <c r="T36">
-        <v>0.8043528068489633</v>
+        <v>0.8145931601926582</v>
       </c>
       <c r="U36">
         <v>0.0543</v>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>6.481357784979964</v>
+        <v>6.296176133980536</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.07561596139392665</v>
+        <v>0.07548836498852772</v>
       </c>
       <c r="C37">
-        <v>904.1338261559981</v>
+        <v>897.1352901940562</v>
       </c>
       <c r="D37">
-        <v>1181.393826155998</v>
+        <v>1186.471290194056</v>
       </c>
       <c r="E37">
-        <v>182.66</v>
+        <v>194.736</v>
       </c>
       <c r="F37">
-        <v>422.66</v>
+        <v>434.736</v>
       </c>
       <c r="G37">
         <v>145.4</v>
@@ -4327,28 +4327,28 @@
         <v>144.5</v>
       </c>
       <c r="M37">
-        <v>22.950438</v>
+        <v>23.6061648</v>
       </c>
       <c r="N37">
-        <v>121.549562</v>
+        <v>120.8938352</v>
       </c>
       <c r="O37">
-        <v>29.17189488</v>
+        <v>29.014520448</v>
       </c>
       <c r="P37">
-        <v>92.37766712</v>
+        <v>91.879314752</v>
       </c>
       <c r="Q37">
-        <v>125.57766712</v>
+        <v>125.079314752</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.09411101752911794</v>
+        <v>0.09473732029457457</v>
       </c>
       <c r="T37">
-        <v>0.8145931601926582</v>
+        <v>0.8251535245783437</v>
       </c>
       <c r="U37">
         <v>0.0543</v>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>6.296176133980536</v>
+        <v>6.121282352481078</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07548836498852771</v>
+        <v>0.07564196858312879</v>
       </c>
       <c r="C38">
-        <v>897.135290194057</v>
+        <v>878.9522448576504</v>
       </c>
       <c r="D38">
-        <v>1186.471290194057</v>
+        <v>1180.36424485765</v>
       </c>
       <c r="E38">
-        <v>194.7359999999999</v>
+        <v>206.812</v>
       </c>
       <c r="F38">
-        <v>434.7359999999999</v>
+        <v>446.812</v>
       </c>
       <c r="G38">
         <v>145.4</v>
@@ -4409,45 +4409,45 @@
         <v>144.5</v>
       </c>
       <c r="M38">
-        <v>23.6061648</v>
+        <v>24.7087036</v>
       </c>
       <c r="N38">
-        <v>120.8938352</v>
+        <v>119.7912964</v>
       </c>
       <c r="O38">
-        <v>29.014520448</v>
+        <v>28.749911136</v>
       </c>
       <c r="P38">
-        <v>91.879314752</v>
+        <v>91.041385264</v>
       </c>
       <c r="Q38">
-        <v>125.079314752</v>
+        <v>124.241385264</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.09473732029457455</v>
+        <v>0.095383505687506</v>
       </c>
       <c r="T38">
-        <v>0.8251535245783435</v>
+        <v>0.8360491386270665</v>
       </c>
       <c r="U38">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V38">
         <v>0.24</v>
       </c>
       <c r="W38">
-        <v>0.041268</v>
+        <v>0.042028</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y38">
-        <v>6.121282352481078</v>
+        <v>5.848141705014422</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.07564196858312879</v>
+        <v>0.07552197217772985</v>
       </c>
       <c r="C39">
-        <v>878.9522448576504</v>
+        <v>871.6417249407814</v>
       </c>
       <c r="D39">
-        <v>1180.36424485765</v>
+        <v>1185.129724940781</v>
       </c>
       <c r="E39">
-        <v>206.812</v>
+        <v>218.888</v>
       </c>
       <c r="F39">
-        <v>446.812</v>
+        <v>458.888</v>
       </c>
       <c r="G39">
         <v>145.4</v>
@@ -4491,28 +4491,28 @@
         <v>144.5</v>
       </c>
       <c r="M39">
-        <v>24.7087036</v>
+        <v>25.3765064</v>
       </c>
       <c r="N39">
-        <v>119.7912964</v>
+        <v>119.1234936</v>
       </c>
       <c r="O39">
-        <v>28.749911136</v>
+        <v>28.589638464</v>
       </c>
       <c r="P39">
-        <v>91.041385264</v>
+        <v>90.533855136</v>
       </c>
       <c r="Q39">
-        <v>124.241385264</v>
+        <v>123.733855136</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.095383505687506</v>
+        <v>0.09605053577053202</v>
       </c>
       <c r="T39">
-        <v>0.8360491386270665</v>
+        <v>0.8472962240967161</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.848141705014422</v>
+        <v>5.69424323909299</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.07552197217772985</v>
+        <v>0.07540197577233092</v>
       </c>
       <c r="C40">
-        <v>871.6417249407814</v>
+        <v>864.3698403153114</v>
       </c>
       <c r="D40">
-        <v>1185.129724940781</v>
+        <v>1189.933840315311</v>
       </c>
       <c r="E40">
-        <v>218.888</v>
+        <v>230.964</v>
       </c>
       <c r="F40">
-        <v>458.888</v>
+        <v>470.964</v>
       </c>
       <c r="G40">
         <v>145.4</v>
@@ -4573,28 +4573,28 @@
         <v>144.5</v>
       </c>
       <c r="M40">
-        <v>25.3765064</v>
+        <v>26.0443092</v>
       </c>
       <c r="N40">
-        <v>119.1234936</v>
+        <v>118.4556908</v>
       </c>
       <c r="O40">
-        <v>28.589638464</v>
+        <v>28.429365792</v>
       </c>
       <c r="P40">
-        <v>90.533855136</v>
+        <v>90.026325008</v>
       </c>
       <c r="Q40">
-        <v>123.733855136</v>
+        <v>123.226325008</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.09605053577053202</v>
+        <v>0.09673943569234576</v>
       </c>
       <c r="T40">
-        <v>0.8472962240967161</v>
+        <v>0.8589120664670099</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>5.69424323909299</v>
+        <v>5.54823700219317</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.07540197577233092</v>
+        <v>0.07528197936693198</v>
       </c>
       <c r="C41">
-        <v>864.3698403153114</v>
+        <v>857.1370627368203</v>
       </c>
       <c r="D41">
-        <v>1189.933840315311</v>
+        <v>1194.77706273682</v>
       </c>
       <c r="E41">
-        <v>230.964</v>
+        <v>243.04</v>
       </c>
       <c r="F41">
-        <v>470.964</v>
+        <v>483.04</v>
       </c>
       <c r="G41">
         <v>145.4</v>
@@ -4655,28 +4655,28 @@
         <v>144.5</v>
       </c>
       <c r="M41">
-        <v>26.0443092</v>
+        <v>26.712112</v>
       </c>
       <c r="N41">
-        <v>118.4556908</v>
+        <v>117.787888</v>
       </c>
       <c r="O41">
-        <v>28.429365792</v>
+        <v>28.26909312</v>
       </c>
       <c r="P41">
-        <v>90.026325008</v>
+        <v>89.51879488</v>
       </c>
       <c r="Q41">
-        <v>123.226325008</v>
+        <v>122.71879488</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.09673943569234576</v>
+        <v>0.09745129894488663</v>
       </c>
       <c r="T41">
-        <v>0.8589120664670099</v>
+        <v>0.8709151035829803</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>5.54823700219317</v>
+        <v>5.409531077138341</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.07528197936693198</v>
+        <v>0.07516198296153304</v>
       </c>
       <c r="C42">
-        <v>857.1370627368203</v>
+        <v>849.9438716727616</v>
       </c>
       <c r="D42">
-        <v>1194.77706273682</v>
+        <v>1199.659871672761</v>
       </c>
       <c r="E42">
-        <v>243.04</v>
+        <v>255.116</v>
       </c>
       <c r="F42">
-        <v>483.04</v>
+        <v>495.116</v>
       </c>
       <c r="G42">
         <v>145.4</v>
@@ -4737,28 +4737,28 @@
         <v>144.5</v>
       </c>
       <c r="M42">
-        <v>26.712112</v>
+        <v>27.3799148</v>
       </c>
       <c r="N42">
-        <v>117.787888</v>
+        <v>117.1200852</v>
       </c>
       <c r="O42">
-        <v>28.26909312</v>
+        <v>28.108820448</v>
       </c>
       <c r="P42">
-        <v>89.51879488</v>
+        <v>89.011264752</v>
       </c>
       <c r="Q42">
-        <v>122.71879488</v>
+        <v>122.211264752</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.09745129894488663</v>
+        <v>0.09818729315514074</v>
       </c>
       <c r="T42">
-        <v>0.8709151035829803</v>
+        <v>0.8833250233130511</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>5.409531077138341</v>
+        <v>5.277591294769113</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.07516198296153304</v>
+        <v>0.07504198655613412</v>
       </c>
       <c r="C43">
-        <v>849.9438716727616</v>
+        <v>842.7907544606912</v>
       </c>
       <c r="D43">
-        <v>1199.659871672761</v>
+        <v>1204.582754460691</v>
       </c>
       <c r="E43">
-        <v>255.116</v>
+        <v>267.192</v>
       </c>
       <c r="F43">
-        <v>495.116</v>
+        <v>507.192</v>
       </c>
       <c r="G43">
         <v>145.4</v>
@@ -4819,28 +4819,28 @@
         <v>144.5</v>
       </c>
       <c r="M43">
-        <v>27.3799148</v>
+        <v>28.0477176</v>
       </c>
       <c r="N43">
-        <v>117.1200852</v>
+        <v>116.4522824</v>
       </c>
       <c r="O43">
-        <v>28.108820448</v>
+        <v>27.948547776</v>
       </c>
       <c r="P43">
-        <v>89.011264752</v>
+        <v>88.503734624</v>
       </c>
       <c r="Q43">
-        <v>122.211264752</v>
+        <v>121.703734624</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.09818729315514074</v>
+        <v>0.09894866647609329</v>
       </c>
       <c r="T43">
-        <v>0.8833250233130511</v>
+        <v>0.8961628713096764</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>5.277591294769113</v>
+        <v>5.151934359179372</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.07504198655613412</v>
+        <v>0.07492199015073518</v>
       </c>
       <c r="C44">
-        <v>842.7907544606912</v>
+        <v>835.6782064704151</v>
       </c>
       <c r="D44">
-        <v>1204.582754460691</v>
+        <v>1209.546206470415</v>
       </c>
       <c r="E44">
-        <v>267.192</v>
+        <v>279.2679999999999</v>
       </c>
       <c r="F44">
-        <v>507.192</v>
+        <v>519.2679999999999</v>
       </c>
       <c r="G44">
         <v>145.4</v>
@@ -4901,28 +4901,28 @@
         <v>144.5</v>
       </c>
       <c r="M44">
-        <v>28.0477176</v>
+        <v>28.7155204</v>
       </c>
       <c r="N44">
-        <v>116.4522824</v>
+        <v>115.7844796</v>
       </c>
       <c r="O44">
-        <v>27.948547776</v>
+        <v>27.788275104</v>
       </c>
       <c r="P44">
-        <v>88.503734624</v>
+        <v>87.996204496</v>
       </c>
       <c r="Q44">
-        <v>121.703734624</v>
+        <v>121.196204496</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.09894866647609329</v>
+        <v>0.0997367546504126</v>
       </c>
       <c r="T44">
-        <v>0.8961628713096763</v>
+        <v>0.9094511701132005</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>5.151934359179372</v>
+        <v>5.032121932221713</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.07492199015073518</v>
+        <v>0.07480199374533625</v>
       </c>
       <c r="C45">
-        <v>835.6782064704151</v>
+        <v>828.6067312701526</v>
       </c>
       <c r="D45">
-        <v>1209.546206470415</v>
+        <v>1214.550731270152</v>
       </c>
       <c r="E45">
-        <v>279.2679999999999</v>
+        <v>291.3439999999999</v>
       </c>
       <c r="F45">
-        <v>519.2679999999999</v>
+        <v>531.3439999999999</v>
       </c>
       <c r="G45">
         <v>145.4</v>
@@ -4983,28 +4983,28 @@
         <v>144.5</v>
       </c>
       <c r="M45">
-        <v>28.7155204</v>
+        <v>29.3833232</v>
       </c>
       <c r="N45">
-        <v>115.7844796</v>
+        <v>115.1166768</v>
       </c>
       <c r="O45">
-        <v>27.788275104</v>
+        <v>27.628002432</v>
       </c>
       <c r="P45">
-        <v>87.996204496</v>
+        <v>87.48867436800001</v>
       </c>
       <c r="Q45">
-        <v>121.196204496</v>
+        <v>120.688674368</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.0997367546504126</v>
+        <v>0.1005529888309576</v>
       </c>
       <c r="T45">
-        <v>0.9094511701132005</v>
+        <v>0.9232140510168506</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>5.032121932221713</v>
+        <v>4.91775552467122</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.07480199374533625</v>
+        <v>0.07468199733993731</v>
       </c>
       <c r="C46">
-        <v>828.6067312701526</v>
+        <v>821.5768407968486</v>
       </c>
       <c r="D46">
-        <v>1214.550731270152</v>
+        <v>1219.596840796848</v>
       </c>
       <c r="E46">
-        <v>291.3439999999999</v>
+        <v>303.42</v>
       </c>
       <c r="F46">
-        <v>531.3439999999999</v>
+        <v>543.42</v>
       </c>
       <c r="G46">
         <v>145.4</v>
@@ -5065,28 +5065,28 @@
         <v>144.5</v>
       </c>
       <c r="M46">
-        <v>29.3833232</v>
+        <v>30.051126</v>
       </c>
       <c r="N46">
-        <v>115.1166768</v>
+        <v>114.448874</v>
       </c>
       <c r="O46">
-        <v>27.628002432</v>
+        <v>27.46772976</v>
       </c>
       <c r="P46">
-        <v>87.48867436800001</v>
+        <v>86.98114424000001</v>
       </c>
       <c r="Q46">
-        <v>120.688674368</v>
+        <v>120.18114424</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1005529888309576</v>
+        <v>0.1013989042544315</v>
       </c>
       <c r="T46">
-        <v>0.9232140510168506</v>
+        <v>0.9374774003169972</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>4.91775552467122</v>
+        <v>4.808472068567414</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.07468199733993731</v>
+        <v>0.07456200093453838</v>
       </c>
       <c r="C47">
-        <v>821.5768407968486</v>
+        <v>814.589055530747</v>
       </c>
       <c r="D47">
-        <v>1219.596840796848</v>
+        <v>1224.685055530747</v>
       </c>
       <c r="E47">
-        <v>303.42</v>
+        <v>315.496</v>
       </c>
       <c r="F47">
-        <v>543.42</v>
+        <v>555.496</v>
       </c>
       <c r="G47">
         <v>145.4</v>
@@ -5147,28 +5147,28 @@
         <v>144.5</v>
       </c>
       <c r="M47">
-        <v>30.051126</v>
+        <v>30.7189288</v>
       </c>
       <c r="N47">
-        <v>114.448874</v>
+        <v>113.7810712</v>
       </c>
       <c r="O47">
-        <v>27.46772976</v>
+        <v>27.307457088</v>
       </c>
       <c r="P47">
-        <v>86.98114424000001</v>
+        <v>86.47361411200001</v>
       </c>
       <c r="Q47">
-        <v>120.18114424</v>
+        <v>119.673614112</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1013989042544315</v>
+        <v>0.1022761498787748</v>
       </c>
       <c r="T47">
-        <v>0.9374774003169972</v>
+        <v>0.9522690218134454</v>
       </c>
       <c r="U47">
         <v>0.0553</v>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>4.808472068567414</v>
+        <v>4.703940067076818</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.07456200093453838</v>
+        <v>0.07444200452913945</v>
       </c>
       <c r="C48">
-        <v>814.589055530747</v>
+        <v>807.6439046743527</v>
       </c>
       <c r="D48">
-        <v>1224.685055530747</v>
+        <v>1229.815904674353</v>
       </c>
       <c r="E48">
-        <v>315.496</v>
+        <v>327.572</v>
       </c>
       <c r="F48">
-        <v>555.496</v>
+        <v>567.572</v>
       </c>
       <c r="G48">
         <v>145.4</v>
@@ -5229,28 +5229,28 @@
         <v>144.5</v>
       </c>
       <c r="M48">
-        <v>30.7189288</v>
+        <v>31.3867316</v>
       </c>
       <c r="N48">
-        <v>113.7810712</v>
+        <v>113.1132684</v>
       </c>
       <c r="O48">
-        <v>27.307457088</v>
+        <v>27.147184416</v>
       </c>
       <c r="P48">
-        <v>86.47361411200001</v>
+        <v>85.96608398399999</v>
       </c>
       <c r="Q48">
-        <v>119.673614112</v>
+        <v>119.166083984</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1022761498787748</v>
+        <v>0.1031864991115838</v>
       </c>
       <c r="T48">
-        <v>0.9522690218134454</v>
+        <v>0.9676188177059859</v>
       </c>
       <c r="U48">
         <v>0.0553</v>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>4.703940067076818</v>
+        <v>4.603856235862418</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.07444200452913945</v>
+        <v>0.07432200812374051</v>
       </c>
       <c r="C49">
-        <v>807.6439046743527</v>
+        <v>800.7419263359103</v>
       </c>
       <c r="D49">
-        <v>1229.815904674353</v>
+        <v>1234.98992633591</v>
       </c>
       <c r="E49">
-        <v>327.572</v>
+        <v>339.648</v>
       </c>
       <c r="F49">
-        <v>567.572</v>
+        <v>579.648</v>
       </c>
       <c r="G49">
         <v>145.4</v>
@@ -5311,28 +5311,28 @@
         <v>144.5</v>
       </c>
       <c r="M49">
-        <v>31.3867316</v>
+        <v>32.0545344</v>
       </c>
       <c r="N49">
-        <v>113.1132684</v>
+        <v>112.4454656</v>
       </c>
       <c r="O49">
-        <v>27.147184416</v>
+        <v>26.986911744</v>
       </c>
       <c r="P49">
-        <v>85.96608398399999</v>
+        <v>85.45855385600001</v>
       </c>
       <c r="Q49">
-        <v>119.166083984</v>
+        <v>118.658553856</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1031864991115838</v>
+        <v>0.104131861776424</v>
       </c>
       <c r="T49">
-        <v>0.9676188177059859</v>
+        <v>0.9835589903636243</v>
       </c>
       <c r="U49">
         <v>0.0553</v>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>4.603856235862418</v>
+        <v>4.507942564281951</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.07432200812374051</v>
+        <v>0.07513301171834157</v>
       </c>
       <c r="C50">
-        <v>800.7419263359104</v>
+        <v>754.5207359554681</v>
       </c>
       <c r="D50">
-        <v>1234.98992633591</v>
+        <v>1200.844735955468</v>
       </c>
       <c r="E50">
-        <v>339.6479999999999</v>
+        <v>351.7239999999999</v>
       </c>
       <c r="F50">
-        <v>579.6479999999999</v>
+        <v>591.7239999999999</v>
       </c>
       <c r="G50">
         <v>145.4</v>
@@ -5393,45 +5393,45 @@
         <v>144.5</v>
       </c>
       <c r="M50">
-        <v>32.05453439999999</v>
+        <v>34.2016472</v>
       </c>
       <c r="N50">
-        <v>112.4454656</v>
+        <v>110.2983528</v>
       </c>
       <c r="O50">
-        <v>26.986911744</v>
+        <v>26.471604672</v>
       </c>
       <c r="P50">
-        <v>85.45855385600001</v>
+        <v>83.82674812800001</v>
       </c>
       <c r="Q50">
-        <v>118.658553856</v>
+        <v>117.026748128</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.104131861776424</v>
+        <v>0.1051142974869442</v>
       </c>
       <c r="T50">
-        <v>0.9835589903636243</v>
+        <v>1.000124267831366</v>
       </c>
       <c r="U50">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V50">
         <v>0.24</v>
       </c>
       <c r="W50">
-        <v>0.042028</v>
+        <v>0.043928</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y50">
-        <v>4.507942564281951</v>
+        <v>4.224942709776856</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.07513301171834157</v>
+        <v>0.07503201531294264</v>
       </c>
       <c r="C51">
-        <v>754.5207359554681</v>
+        <v>746.5936459938409</v>
       </c>
       <c r="D51">
-        <v>1200.844735955468</v>
+        <v>1204.993645993841</v>
       </c>
       <c r="E51">
-        <v>351.7239999999999</v>
+        <v>363.8</v>
       </c>
       <c r="F51">
-        <v>591.7239999999999</v>
+        <v>603.8</v>
       </c>
       <c r="G51">
         <v>145.4</v>
@@ -5475,28 +5475,28 @@
         <v>144.5</v>
       </c>
       <c r="M51">
-        <v>34.2016472</v>
+        <v>34.89964</v>
       </c>
       <c r="N51">
-        <v>110.2983528</v>
+        <v>109.60036</v>
       </c>
       <c r="O51">
-        <v>26.471604672</v>
+        <v>26.3040864</v>
       </c>
       <c r="P51">
-        <v>83.82674812800001</v>
+        <v>83.29627359999999</v>
       </c>
       <c r="Q51">
-        <v>117.026748128</v>
+        <v>116.4962736</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1051142974869442</v>
+        <v>0.1061360306258853</v>
       </c>
       <c r="T51">
-        <v>1.000124267831366</v>
+        <v>1.017352156397818</v>
       </c>
       <c r="U51">
         <v>0.0578</v>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>4.224942709776856</v>
+        <v>4.140443855581319</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.07503201531294264</v>
+        <v>0.07493101890754371</v>
       </c>
       <c r="C52">
-        <v>746.5936459938409</v>
+        <v>738.6953243359605</v>
       </c>
       <c r="D52">
-        <v>1204.993645993841</v>
+        <v>1209.17132433596</v>
       </c>
       <c r="E52">
-        <v>363.8</v>
+        <v>375.876</v>
       </c>
       <c r="F52">
-        <v>603.8</v>
+        <v>615.876</v>
       </c>
       <c r="G52">
         <v>145.4</v>
@@ -5557,28 +5557,28 @@
         <v>144.5</v>
       </c>
       <c r="M52">
-        <v>34.89964</v>
+        <v>35.5976328</v>
       </c>
       <c r="N52">
-        <v>109.60036</v>
+        <v>108.9023672</v>
       </c>
       <c r="O52">
-        <v>26.3040864</v>
+        <v>26.136568128</v>
       </c>
       <c r="P52">
-        <v>83.29627359999999</v>
+        <v>82.76579907199999</v>
       </c>
       <c r="Q52">
-        <v>116.4962736</v>
+        <v>115.965799072</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1061360306258853</v>
+        <v>0.1071994671582525</v>
       </c>
       <c r="T52">
-        <v>1.017352156397818</v>
+        <v>1.03528322408943</v>
       </c>
       <c r="U52">
         <v>0.0578</v>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>4.140443855581319</v>
+        <v>4.059258681942469</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.07493101890754371</v>
+        <v>0.07621322250214477</v>
       </c>
       <c r="C53">
-        <v>738.6953243359605</v>
+        <v>675.6413716233615</v>
       </c>
       <c r="D53">
-        <v>1209.17132433596</v>
+        <v>1158.193371623361</v>
       </c>
       <c r="E53">
-        <v>375.876</v>
+        <v>387.952</v>
       </c>
       <c r="F53">
-        <v>615.876</v>
+        <v>627.952</v>
       </c>
       <c r="G53">
         <v>145.4</v>
@@ -5639,45 +5639,45 @@
         <v>144.5</v>
       </c>
       <c r="M53">
-        <v>35.5976328</v>
+        <v>38.4934576</v>
       </c>
       <c r="N53">
-        <v>108.9023672</v>
+        <v>106.0065424</v>
       </c>
       <c r="O53">
-        <v>26.136568128</v>
+        <v>25.441570176</v>
       </c>
       <c r="P53">
-        <v>82.76579907199999</v>
+        <v>80.564972224</v>
       </c>
       <c r="Q53">
-        <v>115.965799072</v>
+        <v>113.764972224</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1071994671582525</v>
+        <v>0.1083072135461349</v>
       </c>
       <c r="T53">
-        <v>1.03528322408943</v>
+        <v>1.053961419601527</v>
       </c>
       <c r="U53">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V53">
         <v>0.24</v>
       </c>
       <c r="W53">
-        <v>0.043928</v>
+        <v>0.046588</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y53">
-        <v>4.059258681942469</v>
+        <v>3.753884660129882</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.07621322250214477</v>
+        <v>0.07613882609674583</v>
       </c>
       <c r="C54">
-        <v>675.6413716233615</v>
+        <v>666.4054756976223</v>
       </c>
       <c r="D54">
-        <v>1158.193371623361</v>
+        <v>1161.033475697622</v>
       </c>
       <c r="E54">
-        <v>387.952</v>
+        <v>400.028</v>
       </c>
       <c r="F54">
-        <v>627.952</v>
+        <v>640.028</v>
       </c>
       <c r="G54">
         <v>145.4</v>
@@ -5721,28 +5721,28 @@
         <v>144.5</v>
       </c>
       <c r="M54">
-        <v>38.4934576</v>
+        <v>39.2337164</v>
       </c>
       <c r="N54">
-        <v>106.0065424</v>
+        <v>105.2662836</v>
       </c>
       <c r="O54">
-        <v>25.441570176</v>
+        <v>25.263908064</v>
       </c>
       <c r="P54">
-        <v>80.564972224</v>
+        <v>80.002375536</v>
       </c>
       <c r="Q54">
-        <v>113.764972224</v>
+        <v>113.202375536</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1083072135461349</v>
+        <v>0.1094620980781826</v>
       </c>
       <c r="T54">
-        <v>1.053961419601527</v>
+        <v>1.073434431943926</v>
       </c>
       <c r="U54">
         <v>0.0613</v>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.753884660129882</v>
+        <v>3.683056647674601</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.07613882609674583</v>
+        <v>0.07606442969134689</v>
       </c>
       <c r="C55">
-        <v>666.4054756976223</v>
+        <v>657.1835429316873</v>
       </c>
       <c r="D55">
-        <v>1161.033475697622</v>
+        <v>1163.887542931687</v>
       </c>
       <c r="E55">
-        <v>400.028</v>
+        <v>412.104</v>
       </c>
       <c r="F55">
-        <v>640.028</v>
+        <v>652.104</v>
       </c>
       <c r="G55">
         <v>145.4</v>
@@ -5803,28 +5803,28 @@
         <v>144.5</v>
       </c>
       <c r="M55">
-        <v>39.2337164</v>
+        <v>39.97397520000001</v>
       </c>
       <c r="N55">
-        <v>105.2662836</v>
+        <v>104.5260248</v>
       </c>
       <c r="O55">
-        <v>25.263908064</v>
+        <v>25.086245952</v>
       </c>
       <c r="P55">
-        <v>80.002375536</v>
+        <v>79.43977884799999</v>
       </c>
       <c r="Q55">
-        <v>113.202375536</v>
+        <v>112.639778848</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1094620980781826</v>
+        <v>0.1106671949811889</v>
       </c>
       <c r="T55">
-        <v>1.073434431943926</v>
+        <v>1.093754096996863</v>
       </c>
       <c r="U55">
         <v>0.0613</v>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>3.683056647674601</v>
+        <v>3.614851894939885</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.07606442969134689</v>
+        <v>0.07599003328594796</v>
       </c>
       <c r="C56">
-        <v>657.1835429316873</v>
+        <v>647.9756765525607</v>
       </c>
       <c r="D56">
-        <v>1163.887542931687</v>
+        <v>1166.755676552561</v>
       </c>
       <c r="E56">
-        <v>412.104</v>
+        <v>424.1799999999999</v>
       </c>
       <c r="F56">
-        <v>652.104</v>
+        <v>664.1799999999999</v>
       </c>
       <c r="G56">
         <v>145.4</v>
@@ -5885,28 +5885,28 @@
         <v>144.5</v>
       </c>
       <c r="M56">
-        <v>39.97397520000001</v>
+        <v>40.714234</v>
       </c>
       <c r="N56">
-        <v>104.5260248</v>
+        <v>103.785766</v>
       </c>
       <c r="O56">
-        <v>25.086245952</v>
+        <v>24.90858384</v>
       </c>
       <c r="P56">
-        <v>79.43977884799999</v>
+        <v>78.87718215999999</v>
       </c>
       <c r="Q56">
-        <v>112.639778848</v>
+        <v>112.07718216</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1106671949811889</v>
+        <v>0.111925851746551</v>
       </c>
       <c r="T56">
-        <v>1.093754096996863</v>
+        <v>1.114976858274376</v>
       </c>
       <c r="U56">
         <v>0.0613</v>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>3.614851894939885</v>
+        <v>3.549127315031888</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.07599003328594796</v>
+        <v>0.07710731688054902</v>
       </c>
       <c r="C57">
-        <v>647.9756765525607</v>
+        <v>594.2609445815768</v>
       </c>
       <c r="D57">
-        <v>1166.755676552561</v>
+        <v>1125.116944581577</v>
       </c>
       <c r="E57">
-        <v>424.1799999999999</v>
+        <v>436.256</v>
       </c>
       <c r="F57">
-        <v>664.1799999999999</v>
+        <v>676.256</v>
       </c>
       <c r="G57">
         <v>145.4</v>
@@ -5967,45 +5967,45 @@
         <v>144.5</v>
       </c>
       <c r="M57">
-        <v>40.714234</v>
+        <v>43.3480096</v>
       </c>
       <c r="N57">
-        <v>103.785766</v>
+        <v>101.1519904</v>
       </c>
       <c r="O57">
-        <v>24.90858384</v>
+        <v>24.276477696</v>
       </c>
       <c r="P57">
-        <v>78.87718215999999</v>
+        <v>76.87551270399999</v>
       </c>
       <c r="Q57">
-        <v>112.07718216</v>
+        <v>110.075512704</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.111925851746551</v>
+        <v>0.113241720183066</v>
       </c>
       <c r="T57">
-        <v>1.114976858274376</v>
+        <v>1.137164290519048</v>
       </c>
       <c r="U57">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V57">
         <v>0.24</v>
       </c>
       <c r="W57">
-        <v>0.046588</v>
+        <v>0.048716</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y57">
-        <v>3.549127315031888</v>
+        <v>3.333486389188212</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.07710731688054902</v>
+        <v>0.07705420047515009</v>
       </c>
       <c r="C58">
-        <v>594.2609445815768</v>
+        <v>584.0970769299028</v>
       </c>
       <c r="D58">
-        <v>1125.116944581577</v>
+        <v>1127.029076929903</v>
       </c>
       <c r="E58">
-        <v>436.256</v>
+        <v>448.332</v>
       </c>
       <c r="F58">
-        <v>676.256</v>
+        <v>688.332</v>
       </c>
       <c r="G58">
         <v>145.4</v>
@@ -6049,28 +6049,28 @@
         <v>144.5</v>
       </c>
       <c r="M58">
-        <v>43.3480096</v>
+        <v>44.1220812</v>
       </c>
       <c r="N58">
-        <v>101.1519904</v>
+        <v>100.3779188</v>
       </c>
       <c r="O58">
-        <v>24.276477696</v>
+        <v>24.090700512</v>
       </c>
       <c r="P58">
-        <v>76.87551270399999</v>
+        <v>76.28721828800001</v>
       </c>
       <c r="Q58">
-        <v>110.075512704</v>
+        <v>109.487218288</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.113241720183066</v>
+        <v>0.1146187918026746</v>
       </c>
       <c r="T58">
-        <v>1.137164290519048</v>
+        <v>1.160383696356496</v>
       </c>
       <c r="U58">
         <v>0.0641</v>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>3.333486389188212</v>
+        <v>3.275004171834034</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.07705420047515009</v>
+        <v>0.07700108406975115</v>
       </c>
       <c r="C59">
-        <v>584.0970769299028</v>
+        <v>573.9397196672122</v>
       </c>
       <c r="D59">
-        <v>1127.029076929903</v>
+        <v>1128.947719667212</v>
       </c>
       <c r="E59">
-        <v>448.332</v>
+        <v>460.408</v>
       </c>
       <c r="F59">
-        <v>688.332</v>
+        <v>700.408</v>
       </c>
       <c r="G59">
         <v>145.4</v>
@@ -6131,28 +6131,28 @@
         <v>144.5</v>
       </c>
       <c r="M59">
-        <v>44.1220812</v>
+        <v>44.8961528</v>
       </c>
       <c r="N59">
-        <v>100.3779188</v>
+        <v>99.60384719999999</v>
       </c>
       <c r="O59">
-        <v>24.090700512</v>
+        <v>23.904923328</v>
       </c>
       <c r="P59">
-        <v>76.28721828800001</v>
+        <v>75.69892387199999</v>
       </c>
       <c r="Q59">
-        <v>109.487218288</v>
+        <v>108.898923872</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1146187918026746</v>
+        <v>0.1160614382613123</v>
       </c>
       <c r="T59">
-        <v>1.160383696356496</v>
+        <v>1.184708788186203</v>
       </c>
       <c r="U59">
         <v>0.0641</v>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>3.275004171834034</v>
+        <v>3.218538582664481</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.07700108406975116</v>
+        <v>0.07694796766435223</v>
       </c>
       <c r="C60">
-        <v>573.9397196672116</v>
+        <v>563.7889060998618</v>
       </c>
       <c r="D60">
-        <v>1128.947719667211</v>
+        <v>1130.872906099862</v>
       </c>
       <c r="E60">
-        <v>460.4079999999999</v>
+        <v>472.4839999999999</v>
       </c>
       <c r="F60">
-        <v>700.4079999999999</v>
+        <v>712.4839999999999</v>
       </c>
       <c r="G60">
         <v>145.4</v>
@@ -6213,28 +6213,28 @@
         <v>144.5</v>
       </c>
       <c r="M60">
-        <v>44.8961528</v>
+        <v>45.6702244</v>
       </c>
       <c r="N60">
-        <v>99.6038472</v>
+        <v>98.8297756</v>
       </c>
       <c r="O60">
-        <v>23.904923328</v>
+        <v>23.719146144</v>
       </c>
       <c r="P60">
-        <v>75.69892387200001</v>
+        <v>75.110629456</v>
       </c>
       <c r="Q60">
-        <v>108.898923872</v>
+        <v>108.310629456</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1160614382613123</v>
+        <v>0.1175744577179323</v>
       </c>
       <c r="T60">
-        <v>1.184708788186203</v>
+        <v>1.210220469861262</v>
       </c>
       <c r="U60">
         <v>0.0641</v>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>3.218538582664482</v>
+        <v>3.163987081263389</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.07694796766435223</v>
+        <v>0.07689485125895329</v>
       </c>
       <c r="C61">
-        <v>563.7889060998618</v>
+        <v>553.6446697617891</v>
       </c>
       <c r="D61">
-        <v>1130.872906099862</v>
+        <v>1132.804669761789</v>
       </c>
       <c r="E61">
-        <v>472.4839999999999</v>
+        <v>484.5599999999999</v>
       </c>
       <c r="F61">
-        <v>712.4839999999999</v>
+        <v>724.5599999999999</v>
       </c>
       <c r="G61">
         <v>145.4</v>
@@ -6295,28 +6295,28 @@
         <v>144.5</v>
       </c>
       <c r="M61">
-        <v>45.6702244</v>
+        <v>46.444296</v>
       </c>
       <c r="N61">
-        <v>98.8297756</v>
+        <v>98.05570399999999</v>
       </c>
       <c r="O61">
-        <v>23.719146144</v>
+        <v>23.53336896</v>
       </c>
       <c r="P61">
-        <v>75.110629456</v>
+        <v>74.52233504</v>
       </c>
       <c r="Q61">
-        <v>108.310629456</v>
+        <v>107.72233504</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1175744577179323</v>
+        <v>0.1191631281473832</v>
       </c>
       <c r="T61">
-        <v>1.210220469861262</v>
+        <v>1.237007735620073</v>
       </c>
       <c r="U61">
         <v>0.0641</v>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>3.163987081263389</v>
+        <v>3.111253963242332</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.07689485125895329</v>
+        <v>0.07684173485355436</v>
       </c>
       <c r="C62">
-        <v>553.6446697617891</v>
+        <v>543.507044416451</v>
       </c>
       <c r="D62">
-        <v>1132.804669761789</v>
+        <v>1134.743044416451</v>
       </c>
       <c r="E62">
-        <v>484.5599999999999</v>
+        <v>496.636</v>
       </c>
       <c r="F62">
-        <v>724.5599999999999</v>
+        <v>736.636</v>
       </c>
       <c r="G62">
         <v>145.4</v>
@@ -6377,28 +6377,28 @@
         <v>144.5</v>
       </c>
       <c r="M62">
-        <v>46.444296</v>
+        <v>47.2183676</v>
       </c>
       <c r="N62">
-        <v>98.05570399999999</v>
+        <v>97.28163240000001</v>
       </c>
       <c r="O62">
-        <v>23.53336896</v>
+        <v>23.347591776</v>
       </c>
       <c r="P62">
-        <v>74.52233504</v>
+        <v>73.934040624</v>
       </c>
       <c r="Q62">
-        <v>107.72233504</v>
+        <v>107.134040624</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1191631281473832</v>
+        <v>0.1208332688552676</v>
       </c>
       <c r="T62">
-        <v>1.237007735620073</v>
+        <v>1.265168707315235</v>
       </c>
       <c r="U62">
         <v>0.0641</v>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>3.111253963242332</v>
+        <v>3.060249799910491</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.07684173485355436</v>
+        <v>0.07678861844815543</v>
       </c>
       <c r="C63">
-        <v>543.507044416451</v>
+        <v>533.3760640587975</v>
       </c>
       <c r="D63">
-        <v>1134.743044416451</v>
+        <v>1136.688064058797</v>
       </c>
       <c r="E63">
-        <v>496.636</v>
+        <v>508.712</v>
       </c>
       <c r="F63">
-        <v>736.636</v>
+        <v>748.712</v>
       </c>
       <c r="G63">
         <v>145.4</v>
@@ -6459,28 +6459,28 @@
         <v>144.5</v>
       </c>
       <c r="M63">
-        <v>47.2183676</v>
+        <v>47.9924392</v>
       </c>
       <c r="N63">
-        <v>97.28163240000001</v>
+        <v>96.50756079999999</v>
       </c>
       <c r="O63">
-        <v>23.347591776</v>
+        <v>23.161814592</v>
       </c>
       <c r="P63">
-        <v>73.934040624</v>
+        <v>73.34574620799999</v>
       </c>
       <c r="Q63">
-        <v>107.134040624</v>
+        <v>106.545746208</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1208332688552676</v>
+        <v>0.1225913117056722</v>
       </c>
       <c r="T63">
-        <v>1.265168707315235</v>
+        <v>1.294811835415404</v>
       </c>
       <c r="U63">
         <v>0.0641</v>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>3.060249799910491</v>
+        <v>3.010890932169999</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.07678861844815543</v>
+        <v>0.08047014204275649</v>
       </c>
       <c r="C64">
-        <v>533.3760640587975</v>
+        <v>400.598397409348</v>
       </c>
       <c r="D64">
-        <v>1136.688064058797</v>
+        <v>1015.986397409348</v>
       </c>
       <c r="E64">
-        <v>508.712</v>
+        <v>520.7879999999999</v>
       </c>
       <c r="F64">
-        <v>748.712</v>
+        <v>760.7879999999999</v>
       </c>
       <c r="G64">
         <v>145.4</v>
@@ -6541,45 +6541,45 @@
         <v>144.5</v>
       </c>
       <c r="M64">
-        <v>47.9924392</v>
+        <v>54.70065719999999</v>
       </c>
       <c r="N64">
-        <v>96.50756079999999</v>
+        <v>89.79934280000001</v>
       </c>
       <c r="O64">
-        <v>23.161814592</v>
+        <v>21.551842272</v>
       </c>
       <c r="P64">
-        <v>73.34574620799999</v>
+        <v>68.247500528</v>
       </c>
       <c r="Q64">
-        <v>106.545746208</v>
+        <v>101.447500528</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1225913117056722</v>
+        <v>0.1244443838993418</v>
       </c>
       <c r="T64">
-        <v>1.294811835415404</v>
+        <v>1.326057294764231</v>
       </c>
       <c r="U64">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V64">
         <v>0.24</v>
       </c>
       <c r="W64">
-        <v>0.048716</v>
+        <v>0.05464400000000001</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y64">
-        <v>3.010890932169999</v>
+        <v>2.641650162843016</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.08047014204275649</v>
+        <v>0.08047630563735755</v>
       </c>
       <c r="C65">
-        <v>400.598397409348</v>
+        <v>388.3418093057791</v>
       </c>
       <c r="D65">
-        <v>1015.986397409348</v>
+        <v>1015.805809305779</v>
       </c>
       <c r="E65">
-        <v>520.7879999999999</v>
+        <v>532.8639999999999</v>
       </c>
       <c r="F65">
-        <v>760.7879999999999</v>
+        <v>772.8639999999999</v>
       </c>
       <c r="G65">
         <v>145.4</v>
@@ -6623,28 +6623,28 @@
         <v>144.5</v>
       </c>
       <c r="M65">
-        <v>54.70065719999999</v>
+        <v>55.5689216</v>
       </c>
       <c r="N65">
-        <v>89.79934280000001</v>
+        <v>88.9310784</v>
       </c>
       <c r="O65">
-        <v>21.551842272</v>
+        <v>21.343458816</v>
       </c>
       <c r="P65">
-        <v>68.247500528</v>
+        <v>67.58761958400001</v>
       </c>
       <c r="Q65">
-        <v>101.447500528</v>
+        <v>100.787619584</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1244443838993418</v>
+        <v>0.1264004045482154</v>
       </c>
       <c r="T65">
-        <v>1.326057294764231</v>
+        <v>1.359038612965771</v>
       </c>
       <c r="U65">
         <v>0.07190000000000001</v>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.641650162843016</v>
+        <v>2.600374379048594</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.08047630563735755</v>
+        <v>0.08048246923195862</v>
       </c>
       <c r="C66">
-        <v>388.3418093057791</v>
+        <v>376.0852853886353</v>
       </c>
       <c r="D66">
-        <v>1015.805809305779</v>
+        <v>1015.625285388635</v>
       </c>
       <c r="E66">
-        <v>532.8639999999999</v>
+        <v>544.9399999999999</v>
       </c>
       <c r="F66">
-        <v>772.8639999999999</v>
+        <v>784.9399999999999</v>
       </c>
       <c r="G66">
         <v>145.4</v>
@@ -6705,28 +6705,28 @@
         <v>144.5</v>
       </c>
       <c r="M66">
-        <v>55.5689216</v>
+        <v>56.437186</v>
       </c>
       <c r="N66">
-        <v>88.9310784</v>
+        <v>88.062814</v>
       </c>
       <c r="O66">
-        <v>21.343458816</v>
+        <v>21.13507536</v>
       </c>
       <c r="P66">
-        <v>67.58761958400001</v>
+        <v>66.92773864</v>
       </c>
       <c r="Q66">
-        <v>100.787619584</v>
+        <v>100.12773864</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1264004045482154</v>
+        <v>0.1284681978055961</v>
       </c>
       <c r="T66">
-        <v>1.359038612965771</v>
+        <v>1.393904577921685</v>
       </c>
       <c r="U66">
         <v>0.07190000000000001</v>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.600374379048594</v>
+        <v>2.560368619370923</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.08048246923195862</v>
+        <v>0.08048863282655969</v>
       </c>
       <c r="C67">
-        <v>376.0852853886353</v>
+        <v>363.8288256237023</v>
       </c>
       <c r="D67">
-        <v>1015.625285388635</v>
+        <v>1015.444825623702</v>
       </c>
       <c r="E67">
-        <v>544.9399999999999</v>
+        <v>557.016</v>
       </c>
       <c r="F67">
-        <v>784.9399999999999</v>
+        <v>797.016</v>
       </c>
       <c r="G67">
         <v>145.4</v>
@@ -6787,28 +6787,28 @@
         <v>144.5</v>
       </c>
       <c r="M67">
-        <v>56.437186</v>
+        <v>57.30545040000001</v>
       </c>
       <c r="N67">
-        <v>88.062814</v>
+        <v>87.19454959999999</v>
       </c>
       <c r="O67">
-        <v>21.13507536</v>
+        <v>20.92669190399999</v>
       </c>
       <c r="P67">
-        <v>66.92773864</v>
+        <v>66.26785769599999</v>
       </c>
       <c r="Q67">
-        <v>100.12773864</v>
+        <v>99.46785769599998</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1284681978055961</v>
+        <v>0.1306576259604696</v>
       </c>
       <c r="T67">
-        <v>1.393904577921685</v>
+        <v>1.430821481992653</v>
       </c>
       <c r="U67">
         <v>0.07190000000000001</v>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.560368619370923</v>
+        <v>2.52157515544106</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.08048863282655969</v>
+        <v>0.08248067642116075</v>
       </c>
       <c r="C68">
-        <v>363.8288256237023</v>
+        <v>296.6063409370798</v>
       </c>
       <c r="D68">
-        <v>1015.444825623702</v>
+        <v>960.2983409370798</v>
       </c>
       <c r="E68">
-        <v>557.016</v>
+        <v>569.092</v>
       </c>
       <c r="F68">
-        <v>797.016</v>
+        <v>809.092</v>
       </c>
       <c r="G68">
         <v>145.4</v>
@@ -6869,45 +6869,45 @@
         <v>144.5</v>
       </c>
       <c r="M68">
-        <v>57.30545040000001</v>
+        <v>61.3291736</v>
       </c>
       <c r="N68">
-        <v>87.19454959999999</v>
+        <v>83.1708264</v>
       </c>
       <c r="O68">
-        <v>20.92669190399999</v>
+        <v>19.960998336</v>
       </c>
       <c r="P68">
-        <v>66.26785769599999</v>
+        <v>63.20982806399999</v>
       </c>
       <c r="Q68">
-        <v>99.46785769599998</v>
+        <v>96.40982806399998</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1306576259604696</v>
+        <v>0.1329797467307902</v>
       </c>
       <c r="T68">
-        <v>1.430821481992653</v>
+        <v>1.469975774189133</v>
       </c>
       <c r="U68">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V68">
         <v>0.24</v>
       </c>
       <c r="W68">
-        <v>0.05464400000000001</v>
+        <v>0.05760800000000001</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y68">
-        <v>2.52157515544106</v>
+        <v>2.356138058250307</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.08248067642116075</v>
+        <v>0.08251648001576181</v>
       </c>
       <c r="C69">
-        <v>296.6063409370798</v>
+        <v>283.5939185872188</v>
       </c>
       <c r="D69">
-        <v>960.2983409370798</v>
+        <v>959.3619185872188</v>
       </c>
       <c r="E69">
-        <v>569.092</v>
+        <v>581.168</v>
       </c>
       <c r="F69">
-        <v>809.092</v>
+        <v>821.168</v>
       </c>
       <c r="G69">
         <v>145.4</v>
@@ -6951,28 +6951,28 @@
         <v>144.5</v>
       </c>
       <c r="M69">
-        <v>61.3291736</v>
+        <v>62.24453440000001</v>
       </c>
       <c r="N69">
-        <v>83.1708264</v>
+        <v>82.25546559999999</v>
       </c>
       <c r="O69">
-        <v>19.960998336</v>
+        <v>19.741311744</v>
       </c>
       <c r="P69">
-        <v>63.20982806399999</v>
+        <v>62.51415385599999</v>
       </c>
       <c r="Q69">
-        <v>96.40982806399998</v>
+        <v>95.71415385599998</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1329797467307902</v>
+        <v>0.1354470000492557</v>
       </c>
       <c r="T69">
-        <v>1.469975774189133</v>
+        <v>1.511577209647894</v>
       </c>
       <c r="U69">
         <v>0.07580000000000001</v>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.356138058250307</v>
+        <v>2.32148896915839</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.08251648001576181</v>
+        <v>0.08255228361036288</v>
       </c>
       <c r="C70">
-        <v>283.5939185872188</v>
+        <v>270.5833207381994</v>
       </c>
       <c r="D70">
-        <v>959.3619185872188</v>
+        <v>958.4273207381995</v>
       </c>
       <c r="E70">
-        <v>581.168</v>
+        <v>593.244</v>
       </c>
       <c r="F70">
-        <v>821.168</v>
+        <v>833.244</v>
       </c>
       <c r="G70">
         <v>145.4</v>
@@ -7033,28 +7033,28 @@
         <v>144.5</v>
       </c>
       <c r="M70">
-        <v>62.24453440000001</v>
+        <v>63.15989520000001</v>
       </c>
       <c r="N70">
-        <v>82.25546559999999</v>
+        <v>81.34010479999999</v>
       </c>
       <c r="O70">
-        <v>19.741311744</v>
+        <v>19.521625152</v>
       </c>
       <c r="P70">
-        <v>62.51415385599999</v>
+        <v>61.81847964799999</v>
       </c>
       <c r="Q70">
-        <v>95.71415385599998</v>
+        <v>95.01847964799998</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1354470000492557</v>
+        <v>0.1380734310011706</v>
       </c>
       <c r="T70">
-        <v>1.511577209647894</v>
+        <v>1.555862608684639</v>
       </c>
       <c r="U70">
         <v>0.07580000000000001</v>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.32148896915839</v>
+        <v>2.287844201489428</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.08255228361036288</v>
+        <v>0.08258808720496395</v>
       </c>
       <c r="C71">
-        <v>270.5833207381994</v>
+        <v>257.5745420629961</v>
       </c>
       <c r="D71">
-        <v>958.4273207381995</v>
+        <v>957.4945420629962</v>
       </c>
       <c r="E71">
-        <v>593.244</v>
+        <v>605.3200000000001</v>
       </c>
       <c r="F71">
-        <v>833.244</v>
+        <v>845.3200000000001</v>
       </c>
       <c r="G71">
         <v>145.4</v>
@@ -7115,28 +7115,28 @@
         <v>144.5</v>
       </c>
       <c r="M71">
-        <v>63.15989520000001</v>
+        <v>64.07525600000001</v>
       </c>
       <c r="N71">
-        <v>81.34010479999999</v>
+        <v>80.42474399999999</v>
       </c>
       <c r="O71">
-        <v>19.521625152</v>
+        <v>19.30193856</v>
       </c>
       <c r="P71">
-        <v>61.81847964799999</v>
+        <v>61.12280543999999</v>
       </c>
       <c r="Q71">
-        <v>95.01847964799998</v>
+        <v>94.32280543999998</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1380734310011706</v>
+        <v>0.1408749573498798</v>
       </c>
       <c r="T71">
-        <v>1.555862608684639</v>
+        <v>1.603100367657167</v>
       </c>
       <c r="U71">
         <v>0.07580000000000001</v>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.287844201489428</v>
+        <v>2.255160712896722</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.08258808720496395</v>
+        <v>0.08262389079956502</v>
       </c>
       <c r="C72">
-        <v>257.5745420629961</v>
+        <v>244.5675772553024</v>
       </c>
       <c r="D72">
-        <v>957.4945420629962</v>
+        <v>956.5635772553023</v>
       </c>
       <c r="E72">
-        <v>605.3200000000001</v>
+        <v>617.3960000000001</v>
       </c>
       <c r="F72">
-        <v>845.3200000000001</v>
+        <v>857.3960000000001</v>
       </c>
       <c r="G72">
         <v>145.4</v>
@@ -7197,28 +7197,28 @@
         <v>144.5</v>
       </c>
       <c r="M72">
-        <v>64.07525600000001</v>
+        <v>64.99061680000001</v>
       </c>
       <c r="N72">
-        <v>80.42474399999999</v>
+        <v>79.50938319999999</v>
       </c>
       <c r="O72">
-        <v>19.30193856</v>
+        <v>19.082251968</v>
       </c>
       <c r="P72">
-        <v>61.12280543999999</v>
+        <v>60.42713123199999</v>
       </c>
       <c r="Q72">
-        <v>94.32280543999998</v>
+        <v>93.62713123199998</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1408749573498798</v>
+        <v>0.1438696924122932</v>
       </c>
       <c r="T72">
-        <v>1.603100367657167</v>
+        <v>1.65359590311056</v>
       </c>
       <c r="U72">
         <v>0.07580000000000001</v>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.255160712896722</v>
+        <v>2.223397885954514</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.08262389079956502</v>
+        <v>0.08265969439416608</v>
       </c>
       <c r="C73">
-        <v>244.5675772553026</v>
+        <v>231.5624210294276</v>
       </c>
       <c r="D73">
-        <v>956.5635772553023</v>
+        <v>955.6344210294274</v>
       </c>
       <c r="E73">
-        <v>617.3959999999998</v>
+        <v>629.4719999999999</v>
       </c>
       <c r="F73">
-        <v>857.3959999999998</v>
+        <v>869.4719999999999</v>
       </c>
       <c r="G73">
         <v>145.4</v>
@@ -7279,28 +7279,28 @@
         <v>144.5</v>
       </c>
       <c r="M73">
-        <v>64.9906168</v>
+        <v>65.9059776</v>
       </c>
       <c r="N73">
-        <v>79.5093832</v>
+        <v>78.5940224</v>
       </c>
       <c r="O73">
-        <v>19.082251968</v>
+        <v>18.862565376</v>
       </c>
       <c r="P73">
-        <v>60.427131232</v>
+        <v>59.731457024</v>
       </c>
       <c r="Q73">
-        <v>93.62713123199998</v>
+        <v>92.931457024</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1438696924122931</v>
+        <v>0.1470783371220217</v>
       </c>
       <c r="T73">
-        <v>1.653595903110559</v>
+        <v>1.707698262524908</v>
       </c>
       <c r="U73">
         <v>0.07580000000000001</v>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.223397885954515</v>
+        <v>2.192517359760703</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.08265969439416608</v>
+        <v>0.08269549798876714</v>
       </c>
       <c r="C74">
-        <v>231.5624210294276</v>
+        <v>218.5590681201978</v>
       </c>
       <c r="D74">
-        <v>955.6344210294274</v>
+        <v>954.7070681201976</v>
       </c>
       <c r="E74">
-        <v>629.4719999999999</v>
+        <v>641.5479999999999</v>
       </c>
       <c r="F74">
-        <v>869.4719999999999</v>
+        <v>881.5479999999999</v>
       </c>
       <c r="G74">
         <v>145.4</v>
@@ -7361,28 +7361,28 @@
         <v>144.5</v>
       </c>
       <c r="M74">
-        <v>65.9059776</v>
+        <v>66.8213384</v>
       </c>
       <c r="N74">
-        <v>78.5940224</v>
+        <v>77.6786616</v>
       </c>
       <c r="O74">
-        <v>18.862565376</v>
+        <v>18.642878784</v>
       </c>
       <c r="P74">
-        <v>59.731457024</v>
+        <v>59.03578281599999</v>
       </c>
       <c r="Q74">
-        <v>92.931457024</v>
+        <v>92.23578281599998</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1470783371220217</v>
+        <v>0.1505246592176561</v>
       </c>
       <c r="T74">
-        <v>1.707698262524908</v>
+        <v>1.765808204118097</v>
       </c>
       <c r="U74">
         <v>0.07580000000000001</v>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.192517359760703</v>
+        <v>2.162482875380419</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.08269549798876714</v>
+        <v>0.08273130158336821</v>
       </c>
       <c r="C75">
-        <v>218.5590681201978</v>
+        <v>205.5575132828579</v>
       </c>
       <c r="D75">
-        <v>954.7070681201976</v>
+        <v>953.7815132828578</v>
       </c>
       <c r="E75">
-        <v>641.5479999999999</v>
+        <v>653.6239999999999</v>
       </c>
       <c r="F75">
-        <v>881.5479999999999</v>
+        <v>893.6239999999999</v>
       </c>
       <c r="G75">
         <v>145.4</v>
@@ -7443,28 +7443,28 @@
         <v>144.5</v>
       </c>
       <c r="M75">
-        <v>66.8213384</v>
+        <v>67.7366992</v>
       </c>
       <c r="N75">
-        <v>77.6786616</v>
+        <v>76.7633008</v>
       </c>
       <c r="O75">
-        <v>18.642878784</v>
+        <v>18.423192192</v>
       </c>
       <c r="P75">
-        <v>59.03578281599999</v>
+        <v>58.34010860799999</v>
       </c>
       <c r="Q75">
-        <v>92.23578281599998</v>
+        <v>91.54010860799998</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1505246592176561</v>
+        <v>0.1542360830129546</v>
       </c>
       <c r="T75">
-        <v>1.765808204118097</v>
+        <v>1.828388141218455</v>
       </c>
       <c r="U75">
         <v>0.07580000000000001</v>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.162482875380419</v>
+        <v>2.133260133821224</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.08273130158336821</v>
+        <v>0.08276710517796929</v>
       </c>
       <c r="C76">
-        <v>205.5575132828579</v>
+        <v>192.5577512929705</v>
       </c>
       <c r="D76">
-        <v>953.7815132828578</v>
+        <v>952.8577512929703</v>
       </c>
       <c r="E76">
-        <v>653.6239999999999</v>
+        <v>665.6999999999999</v>
       </c>
       <c r="F76">
-        <v>893.6239999999999</v>
+        <v>905.6999999999999</v>
       </c>
       <c r="G76">
         <v>145.4</v>
@@ -7525,28 +7525,28 @@
         <v>144.5</v>
       </c>
       <c r="M76">
-        <v>67.7366992</v>
+        <v>68.65206000000001</v>
       </c>
       <c r="N76">
-        <v>76.7633008</v>
+        <v>75.84793999999999</v>
       </c>
       <c r="O76">
-        <v>18.423192192</v>
+        <v>18.2035056</v>
       </c>
       <c r="P76">
-        <v>58.34010860799999</v>
+        <v>57.64443439999999</v>
       </c>
       <c r="Q76">
-        <v>91.54010860799998</v>
+        <v>90.84443439999998</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1542360830129546</v>
+        <v>0.1582444207118771</v>
       </c>
       <c r="T76">
-        <v>1.828388141218455</v>
+        <v>1.895974473286842</v>
       </c>
       <c r="U76">
         <v>0.07580000000000001</v>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.133260133821224</v>
+        <v>2.104816665370274</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.08276710517796929</v>
+        <v>0.08280290877257035</v>
       </c>
       <c r="C77">
-        <v>192.5577512929705</v>
+        <v>179.5597769463194</v>
       </c>
       <c r="D77">
-        <v>952.8577512929703</v>
+        <v>951.9357769463194</v>
       </c>
       <c r="E77">
-        <v>665.6999999999999</v>
+        <v>677.776</v>
       </c>
       <c r="F77">
-        <v>905.6999999999999</v>
+        <v>917.776</v>
       </c>
       <c r="G77">
         <v>145.4</v>
@@ -7607,28 +7607,28 @@
         <v>144.5</v>
       </c>
       <c r="M77">
-        <v>68.65206000000001</v>
+        <v>69.56742080000001</v>
       </c>
       <c r="N77">
-        <v>75.84793999999999</v>
+        <v>74.93257919999999</v>
       </c>
       <c r="O77">
-        <v>18.2035056</v>
+        <v>17.983819008</v>
       </c>
       <c r="P77">
-        <v>57.64443439999999</v>
+        <v>56.94876019199999</v>
       </c>
       <c r="Q77">
-        <v>90.84443439999998</v>
+        <v>90.14876019199998</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1582444207118771</v>
+        <v>0.1625867865523764</v>
       </c>
       <c r="T77">
-        <v>1.895974473286842</v>
+        <v>1.969192999694261</v>
       </c>
       <c r="U77">
         <v>0.07580000000000001</v>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>2.104816665370274</v>
+        <v>2.077121709246981</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.08280290877257035</v>
+        <v>0.08283871236717141</v>
       </c>
       <c r="C78">
-        <v>179.5597769463194</v>
+        <v>166.5635850588109</v>
       </c>
       <c r="D78">
-        <v>951.9357769463194</v>
+        <v>951.0155850588108</v>
       </c>
       <c r="E78">
-        <v>677.776</v>
+        <v>689.852</v>
       </c>
       <c r="F78">
-        <v>917.776</v>
+        <v>929.852</v>
       </c>
       <c r="G78">
         <v>145.4</v>
@@ -7689,28 +7689,28 @@
         <v>144.5</v>
       </c>
       <c r="M78">
-        <v>69.56742080000001</v>
+        <v>70.48278160000001</v>
       </c>
       <c r="N78">
-        <v>74.93257919999999</v>
+        <v>74.01721839999999</v>
       </c>
       <c r="O78">
-        <v>17.983819008</v>
+        <v>17.764132416</v>
       </c>
       <c r="P78">
-        <v>56.94876019199999</v>
+        <v>56.25308598399999</v>
       </c>
       <c r="Q78">
-        <v>90.14876019199998</v>
+        <v>89.45308598399998</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1625867865523764</v>
+        <v>0.1673067494224844</v>
       </c>
       <c r="T78">
-        <v>1.969192999694261</v>
+        <v>2.048778354484933</v>
       </c>
       <c r="U78">
         <v>0.07580000000000001</v>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>2.077121709246981</v>
+        <v>2.050146102633384</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.08283871236717141</v>
+        <v>0.08287451596177248</v>
       </c>
       <c r="C79">
-        <v>166.5635850588109</v>
+        <v>153.5691704663762</v>
       </c>
       <c r="D79">
-        <v>951.0155850588108</v>
+        <v>950.0971704663763</v>
       </c>
       <c r="E79">
-        <v>689.852</v>
+        <v>701.928</v>
       </c>
       <c r="F79">
-        <v>929.852</v>
+        <v>941.928</v>
       </c>
       <c r="G79">
         <v>145.4</v>
@@ -7771,28 +7771,28 @@
         <v>144.5</v>
       </c>
       <c r="M79">
-        <v>70.48278160000001</v>
+        <v>71.39814240000001</v>
       </c>
       <c r="N79">
-        <v>74.01721839999999</v>
+        <v>73.10185759999999</v>
       </c>
       <c r="O79">
-        <v>17.764132416</v>
+        <v>17.544445824</v>
       </c>
       <c r="P79">
-        <v>56.25308598399999</v>
+        <v>55.557411776</v>
       </c>
       <c r="Q79">
-        <v>89.45308598399998</v>
+        <v>88.75741177599998</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1673067494224844</v>
+        <v>0.1724557998262385</v>
       </c>
       <c r="T79">
-        <v>2.048778354484933</v>
+        <v>2.135598741529303</v>
       </c>
       <c r="U79">
         <v>0.07580000000000001</v>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>2.050146102633384</v>
+        <v>2.023862178240648</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.08287451596177248</v>
+        <v>0.09143599955637355</v>
       </c>
       <c r="C80">
-        <v>153.5691704663762</v>
+        <v>-36.74859956819171</v>
       </c>
       <c r="D80">
-        <v>950.0971704663763</v>
+        <v>771.8554004318083</v>
       </c>
       <c r="E80">
-        <v>701.928</v>
+        <v>714.004</v>
       </c>
       <c r="F80">
-        <v>941.928</v>
+        <v>954.004</v>
       </c>
       <c r="G80">
         <v>145.4</v>
@@ -7853,45 +7853,45 @@
         <v>144.5</v>
       </c>
       <c r="M80">
-        <v>71.39814240000001</v>
+        <v>85.86036</v>
       </c>
       <c r="N80">
-        <v>73.10185759999999</v>
+        <v>58.63964</v>
       </c>
       <c r="O80">
-        <v>17.544445824</v>
+        <v>14.0735136</v>
       </c>
       <c r="P80">
-        <v>55.557411776</v>
+        <v>44.5661264</v>
       </c>
       <c r="Q80">
-        <v>88.75741177599998</v>
+        <v>77.76612639999999</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1724557998262385</v>
+        <v>0.1780952359827311</v>
       </c>
       <c r="T80">
-        <v>2.135598741529303</v>
+        <v>2.230687736863613</v>
       </c>
       <c r="U80">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V80">
         <v>0.24</v>
       </c>
       <c r="W80">
-        <v>0.05760800000000001</v>
+        <v>0.0684</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y80">
-        <v>2.023862178240648</v>
+        <v>1.682965223998595</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.09143599955637355</v>
+        <v>0.09157972315097461</v>
       </c>
       <c r="C81">
-        <v>-36.74859956819171</v>
+        <v>-51.24780847001182</v>
       </c>
       <c r="D81">
-        <v>771.8554004318083</v>
+        <v>769.4321915299881</v>
       </c>
       <c r="E81">
-        <v>714.004</v>
+        <v>726.0799999999999</v>
       </c>
       <c r="F81">
-        <v>954.004</v>
+        <v>966.0799999999999</v>
       </c>
       <c r="G81">
         <v>145.4</v>
@@ -7935,28 +7935,28 @@
         <v>144.5</v>
       </c>
       <c r="M81">
-        <v>85.86036</v>
+        <v>86.9472</v>
       </c>
       <c r="N81">
-        <v>58.63964</v>
+        <v>57.5528</v>
       </c>
       <c r="O81">
-        <v>14.0735136</v>
+        <v>13.812672</v>
       </c>
       <c r="P81">
-        <v>44.5661264</v>
+        <v>43.74012800000001</v>
       </c>
       <c r="Q81">
-        <v>77.76612639999999</v>
+        <v>76.94012799999999</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1780952359827311</v>
+        <v>0.1842986157548731</v>
       </c>
       <c r="T81">
-        <v>2.230687736863613</v>
+        <v>2.335285631731355</v>
       </c>
       <c r="U81">
         <v>0.09</v>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>1.682965223998595</v>
+        <v>1.661928158698613</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.09157972315097461</v>
+        <v>0.09172344674557567</v>
       </c>
       <c r="C82">
-        <v>-51.24780847001182</v>
+        <v>-65.73184985638966</v>
       </c>
       <c r="D82">
-        <v>769.4321915299881</v>
+        <v>767.0241501436103</v>
       </c>
       <c r="E82">
-        <v>726.0799999999999</v>
+        <v>738.1559999999999</v>
       </c>
       <c r="F82">
-        <v>966.0799999999999</v>
+        <v>978.1559999999999</v>
       </c>
       <c r="G82">
         <v>145.4</v>
@@ -8017,28 +8017,28 @@
         <v>144.5</v>
       </c>
       <c r="M82">
-        <v>86.9472</v>
+        <v>88.03403999999999</v>
       </c>
       <c r="N82">
-        <v>57.5528</v>
+        <v>56.46596000000001</v>
       </c>
       <c r="O82">
-        <v>13.812672</v>
+        <v>13.5518304</v>
       </c>
       <c r="P82">
-        <v>43.74012800000001</v>
+        <v>42.91412960000001</v>
       </c>
       <c r="Q82">
-        <v>76.94012799999999</v>
+        <v>76.1141296</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1842986157548731</v>
+        <v>0.1911549828714509</v>
       </c>
       <c r="T82">
-        <v>2.335285631731355</v>
+        <v>2.450893831322016</v>
       </c>
       <c r="U82">
         <v>0.09</v>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>1.661928158698613</v>
+        <v>1.641410527109741</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.09172344674557567</v>
+        <v>0.09186717034017673</v>
       </c>
       <c r="C83">
-        <v>-65.73184985638966</v>
+        <v>-80.20086568936608</v>
       </c>
       <c r="D83">
-        <v>767.0241501436103</v>
+        <v>764.6311343106339</v>
       </c>
       <c r="E83">
-        <v>738.1559999999999</v>
+        <v>750.232</v>
       </c>
       <c r="F83">
-        <v>978.1559999999999</v>
+        <v>990.232</v>
       </c>
       <c r="G83">
         <v>145.4</v>
@@ -8099,28 +8099,28 @@
         <v>144.5</v>
       </c>
       <c r="M83">
-        <v>88.03403999999999</v>
+        <v>89.12088</v>
       </c>
       <c r="N83">
-        <v>56.46596000000001</v>
+        <v>55.37912</v>
       </c>
       <c r="O83">
-        <v>13.5518304</v>
+        <v>13.2909888</v>
       </c>
       <c r="P83">
-        <v>42.91412960000001</v>
+        <v>42.0881312</v>
       </c>
       <c r="Q83">
-        <v>76.1141296</v>
+        <v>75.28813119999998</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1911549828714509</v>
+        <v>0.1987731685565374</v>
       </c>
       <c r="T83">
-        <v>2.450893831322016</v>
+        <v>2.57934738642275</v>
       </c>
       <c r="U83">
         <v>0.09</v>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>1.641410527109741</v>
+        <v>1.621393325559622</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.09186717034017673</v>
+        <v>0.09201089393477779</v>
       </c>
       <c r="C84">
-        <v>-80.20086568936608</v>
+        <v>-94.65499616487932</v>
       </c>
       <c r="D84">
-        <v>764.6311343106339</v>
+        <v>762.2530038351207</v>
       </c>
       <c r="E84">
-        <v>750.232</v>
+        <v>762.308</v>
       </c>
       <c r="F84">
-        <v>990.232</v>
+        <v>1002.308</v>
       </c>
       <c r="G84">
         <v>145.4</v>
@@ -8181,28 +8181,28 @@
         <v>144.5</v>
       </c>
       <c r="M84">
-        <v>89.12088</v>
+        <v>90.20771999999999</v>
       </c>
       <c r="N84">
-        <v>55.37912</v>
+        <v>54.29228000000001</v>
       </c>
       <c r="O84">
-        <v>13.2909888</v>
+        <v>13.0301472</v>
       </c>
       <c r="P84">
-        <v>42.0881312</v>
+        <v>41.2621328</v>
       </c>
       <c r="Q84">
-        <v>75.28813119999998</v>
+        <v>74.46213279999999</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1987731685565374</v>
+        <v>0.2072876113810459</v>
       </c>
       <c r="T84">
-        <v>2.57934738642275</v>
+        <v>2.722913124476513</v>
       </c>
       <c r="U84">
         <v>0.09</v>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>1.621393325559622</v>
+        <v>1.60185846621553</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.09201089393477779</v>
+        <v>0.09215461752937887</v>
       </c>
       <c r="C85">
-        <v>-94.65499616487932</v>
+        <v>-109.0943797401451</v>
       </c>
       <c r="D85">
-        <v>762.2530038351207</v>
+        <v>759.889620259855</v>
       </c>
       <c r="E85">
-        <v>762.308</v>
+        <v>774.384</v>
       </c>
       <c r="F85">
-        <v>1002.308</v>
+        <v>1014.384</v>
       </c>
       <c r="G85">
         <v>145.4</v>
@@ -8263,28 +8263,28 @@
         <v>144.5</v>
       </c>
       <c r="M85">
-        <v>90.20771999999999</v>
+        <v>91.29456</v>
       </c>
       <c r="N85">
-        <v>54.29228000000001</v>
+        <v>53.20544</v>
       </c>
       <c r="O85">
-        <v>13.0301472</v>
+        <v>12.7693056</v>
       </c>
       <c r="P85">
-        <v>41.2621328</v>
+        <v>40.4361344</v>
       </c>
       <c r="Q85">
-        <v>74.46213279999999</v>
+        <v>73.63613439999999</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2072876113810459</v>
+        <v>0.216866359558618</v>
       </c>
       <c r="T85">
-        <v>2.722913124476513</v>
+        <v>2.884424579786996</v>
       </c>
       <c r="U85">
         <v>0.09</v>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>1.60185846621553</v>
+        <v>1.582788722570107</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.09215461752937887</v>
+        <v>0.09229834112397994</v>
       </c>
       <c r="C86">
-        <v>-109.094379740145</v>
+        <v>-123.5191531605253</v>
       </c>
       <c r="D86">
-        <v>759.889620259855</v>
+        <v>757.5408468394745</v>
       </c>
       <c r="E86">
-        <v>774.3839999999999</v>
+        <v>786.4599999999998</v>
       </c>
       <c r="F86">
-        <v>1014.384</v>
+        <v>1026.46</v>
       </c>
       <c r="G86">
         <v>145.4</v>
@@ -8345,28 +8345,28 @@
         <v>144.5</v>
       </c>
       <c r="M86">
-        <v>91.29455999999999</v>
+        <v>92.38139999999999</v>
       </c>
       <c r="N86">
-        <v>53.20544000000001</v>
+        <v>52.11860000000001</v>
       </c>
       <c r="O86">
-        <v>12.7693056</v>
+        <v>12.508464</v>
       </c>
       <c r="P86">
-        <v>40.43613440000001</v>
+        <v>39.61013600000001</v>
       </c>
       <c r="Q86">
-        <v>73.6361344</v>
+        <v>72.810136</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2168663595586179</v>
+        <v>0.2277222741598662</v>
       </c>
       <c r="T86">
-        <v>2.884424579786994</v>
+        <v>3.067470895805541</v>
       </c>
       <c r="U86">
         <v>0.09</v>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>1.582788722570107</v>
+        <v>1.564167678775165</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.09229834112397994</v>
+        <v>0.09244206471858099</v>
       </c>
       <c r="C87">
-        <v>-123.5191531605253</v>
+        <v>-137.9294514859063</v>
       </c>
       <c r="D87">
-        <v>757.5408468394745</v>
+        <v>755.2065485140936</v>
       </c>
       <c r="E87">
-        <v>786.4599999999998</v>
+        <v>798.5359999999998</v>
       </c>
       <c r="F87">
-        <v>1026.46</v>
+        <v>1038.536</v>
       </c>
       <c r="G87">
         <v>145.4</v>
@@ -8427,28 +8427,28 @@
         <v>144.5</v>
       </c>
       <c r="M87">
-        <v>92.38139999999999</v>
+        <v>93.46823999999998</v>
       </c>
       <c r="N87">
-        <v>52.11860000000001</v>
+        <v>51.03176000000002</v>
       </c>
       <c r="O87">
-        <v>12.508464</v>
+        <v>12.2476224</v>
       </c>
       <c r="P87">
-        <v>39.61013600000001</v>
+        <v>38.78413760000002</v>
       </c>
       <c r="Q87">
-        <v>72.810136</v>
+        <v>71.9841376</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2277222741598662</v>
+        <v>0.24012903370415</v>
       </c>
       <c r="T87">
-        <v>3.067470895805541</v>
+        <v>3.276666685541023</v>
       </c>
       <c r="U87">
         <v>0.09</v>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>1.564167678775165</v>
+        <v>1.545979682510338</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.09244206471858099</v>
+        <v>0.09258578831318207</v>
       </c>
       <c r="C88">
-        <v>-137.9294514859063</v>
+        <v>-152.3254081165853</v>
       </c>
       <c r="D88">
-        <v>755.2065485140936</v>
+        <v>752.8865918834146</v>
       </c>
       <c r="E88">
-        <v>798.5359999999998</v>
+        <v>810.6119999999999</v>
       </c>
       <c r="F88">
-        <v>1038.536</v>
+        <v>1050.612</v>
       </c>
       <c r="G88">
         <v>145.4</v>
@@ -8509,28 +8509,28 @@
         <v>144.5</v>
       </c>
       <c r="M88">
-        <v>93.46823999999998</v>
+        <v>94.55507999999999</v>
       </c>
       <c r="N88">
-        <v>51.03176000000002</v>
+        <v>49.94492000000001</v>
       </c>
       <c r="O88">
-        <v>12.2476224</v>
+        <v>11.9867808</v>
       </c>
       <c r="P88">
-        <v>38.78413760000002</v>
+        <v>37.95813920000001</v>
       </c>
       <c r="Q88">
-        <v>71.9841376</v>
+        <v>71.15813919999999</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.24012903370415</v>
+        <v>0.2544445254860158</v>
       </c>
       <c r="T88">
-        <v>3.276666685541023</v>
+        <v>3.518046442928117</v>
       </c>
       <c r="U88">
         <v>0.09</v>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>1.545979682510338</v>
+        <v>1.528209801102173</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.09258578831318207</v>
+        <v>0.09272951190778314</v>
       </c>
       <c r="C89">
-        <v>-152.3254081165853</v>
+        <v>-166.7071548186833</v>
       </c>
       <c r="D89">
-        <v>752.8865918834146</v>
+        <v>750.5808451813166</v>
       </c>
       <c r="E89">
-        <v>810.6119999999999</v>
+        <v>822.6879999999999</v>
       </c>
       <c r="F89">
-        <v>1050.612</v>
+        <v>1062.688</v>
       </c>
       <c r="G89">
         <v>145.4</v>
@@ -8591,28 +8591,28 @@
         <v>144.5</v>
       </c>
       <c r="M89">
-        <v>94.55507999999999</v>
+        <v>95.64191999999998</v>
       </c>
       <c r="N89">
-        <v>49.94492000000001</v>
+        <v>48.85808000000002</v>
       </c>
       <c r="O89">
-        <v>11.9867808</v>
+        <v>11.7259392</v>
       </c>
       <c r="P89">
-        <v>37.95813920000001</v>
+        <v>37.13214080000002</v>
       </c>
       <c r="Q89">
-        <v>71.15813919999999</v>
+        <v>70.3321408</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2544445254860158</v>
+        <v>0.2711459325648594</v>
       </c>
       <c r="T89">
-        <v>3.518046442928117</v>
+        <v>3.799656159879728</v>
       </c>
       <c r="U89">
         <v>0.09</v>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>1.528209801102173</v>
+        <v>1.510843780635102</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.09272951190778314</v>
+        <v>0.1345472468405723</v>
       </c>
       <c r="C90">
-        <v>-166.7071548186833</v>
+        <v>-532.4571215819182</v>
       </c>
       <c r="D90">
-        <v>750.5808451813166</v>
+        <v>396.9068784180818</v>
       </c>
       <c r="E90">
-        <v>822.6879999999999</v>
+        <v>834.7639999999999</v>
       </c>
       <c r="F90">
-        <v>1062.688</v>
+        <v>1074.764</v>
       </c>
       <c r="G90">
         <v>145.4</v>
@@ -8673,45 +8673,45 @@
         <v>144.5</v>
       </c>
       <c r="M90">
-        <v>95.64191999999998</v>
+        <v>157.7753552</v>
       </c>
       <c r="N90">
-        <v>48.85808000000002</v>
+        <v>-13.27535520000001</v>
       </c>
       <c r="O90">
-        <v>11.7259392</v>
+        <v>-3.186085248000002</v>
       </c>
       <c r="P90">
-        <v>37.13214080000002</v>
+        <v>-10.08926995200001</v>
       </c>
       <c r="Q90">
-        <v>70.3321408</v>
+        <v>23.11073004799998</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2711459325648594</v>
+        <v>0.2964851402080393</v>
       </c>
       <c r="T90">
-        <v>3.799656159879728</v>
+        <v>4.226911603596993</v>
       </c>
       <c r="U90">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V90">
-        <v>0.24</v>
+        <v>0.219806191886171</v>
       </c>
       <c r="W90">
-        <v>0.0684</v>
+        <v>0.1145324510311101</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y90">
-        <v>1.510843780635102</v>
+        <v>0.9158591328590461</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1345472468405723</v>
+        <v>0.1355572468405723</v>
       </c>
       <c r="C91">
-        <v>-532.4571215819182</v>
+        <v>-548.9993453277768</v>
       </c>
       <c r="D91">
-        <v>396.9068784180818</v>
+        <v>392.4406546722231</v>
       </c>
       <c r="E91">
-        <v>834.7639999999999</v>
+        <v>846.8399999999999</v>
       </c>
       <c r="F91">
-        <v>1074.764</v>
+        <v>1086.84</v>
       </c>
       <c r="G91">
         <v>145.4</v>
@@ -8755,37 +8755,37 @@
         <v>144.5</v>
       </c>
       <c r="M91">
-        <v>157.7753552</v>
+        <v>159.548112</v>
       </c>
       <c r="N91">
-        <v>-13.27535520000001</v>
+        <v>-15.048112</v>
       </c>
       <c r="O91">
-        <v>-3.186085248000002</v>
+        <v>-3.611546880000001</v>
       </c>
       <c r="P91">
-        <v>-10.08926995200001</v>
+        <v>-11.43656512</v>
       </c>
       <c r="Q91">
-        <v>23.11073004799998</v>
+        <v>21.76343487999998</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2964851402080393</v>
+        <v>0.3215536542288431</v>
       </c>
       <c r="T91">
-        <v>4.226911603596993</v>
+        <v>4.649602763956691</v>
       </c>
       <c r="U91">
         <v>0.1468</v>
       </c>
       <c r="V91">
-        <v>0.219806191886171</v>
+        <v>0.2173639008652136</v>
       </c>
       <c r="W91">
-        <v>0.1145324510311101</v>
+        <v>0.1148909793529867</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.9158591328590461</v>
+        <v>0.9056829202717234</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1355572468405723</v>
+        <v>0.1365672468405723</v>
       </c>
       <c r="C92">
-        <v>-548.9993453277768</v>
+        <v>-565.4421744981618</v>
       </c>
       <c r="D92">
-        <v>392.4406546722231</v>
+        <v>388.0738255018381</v>
       </c>
       <c r="E92">
-        <v>846.8399999999999</v>
+        <v>858.9159999999999</v>
       </c>
       <c r="F92">
-        <v>1086.84</v>
+        <v>1098.916</v>
       </c>
       <c r="G92">
         <v>145.4</v>
@@ -8837,37 +8837,37 @@
         <v>144.5</v>
       </c>
       <c r="M92">
-        <v>159.548112</v>
+        <v>161.3208688</v>
       </c>
       <c r="N92">
-        <v>-15.048112</v>
+        <v>-16.8208688</v>
       </c>
       <c r="O92">
-        <v>-3.611546880000001</v>
+        <v>-4.037008512</v>
       </c>
       <c r="P92">
-        <v>-11.43656512</v>
+        <v>-12.783860288</v>
       </c>
       <c r="Q92">
-        <v>21.76343487999998</v>
+        <v>20.41613971199999</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3215536542288431</v>
+        <v>0.3521929491431592</v>
       </c>
       <c r="T92">
-        <v>4.649602763956691</v>
+        <v>5.166225293285215</v>
       </c>
       <c r="U92">
         <v>0.1468</v>
       </c>
       <c r="V92">
-        <v>0.2173639008652136</v>
+        <v>0.2149752865699915</v>
       </c>
       <c r="W92">
-        <v>0.1148909793529867</v>
+        <v>0.1152416279315253</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.9056829202717234</v>
+        <v>0.8957303607082979</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1365672468405723</v>
+        <v>0.1375772468405723</v>
       </c>
       <c r="C93">
-        <v>-565.4421744981618</v>
+        <v>-581.7888905770362</v>
       </c>
       <c r="D93">
-        <v>388.0738255018381</v>
+        <v>383.8031094229638</v>
       </c>
       <c r="E93">
-        <v>858.9159999999999</v>
+        <v>870.992</v>
       </c>
       <c r="F93">
-        <v>1098.916</v>
+        <v>1110.992</v>
       </c>
       <c r="G93">
         <v>145.4</v>
@@ -8919,37 +8919,37 @@
         <v>144.5</v>
       </c>
       <c r="M93">
-        <v>161.3208688</v>
+        <v>163.0936256</v>
       </c>
       <c r="N93">
-        <v>-16.8208688</v>
+        <v>-18.5936256</v>
       </c>
       <c r="O93">
-        <v>-4.037008512</v>
+        <v>-4.462470143999999</v>
       </c>
       <c r="P93">
-        <v>-12.783860288</v>
+        <v>-14.131155456</v>
       </c>
       <c r="Q93">
-        <v>20.41613971199999</v>
+        <v>19.06884454399999</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3521929491431592</v>
+        <v>0.3904920677860541</v>
       </c>
       <c r="T93">
-        <v>5.166225293285215</v>
+        <v>5.812003454945867</v>
       </c>
       <c r="U93">
         <v>0.1468</v>
       </c>
       <c r="V93">
-        <v>0.2149752865699915</v>
+        <v>0.2126385986724916</v>
       </c>
       <c r="W93">
-        <v>0.1152416279315253</v>
+        <v>0.1155846537148782</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.8957303607082979</v>
+        <v>0.8859941611353817</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1375772468405723</v>
+        <v>0.1385872468405723</v>
       </c>
       <c r="C94">
-        <v>-581.7888905770362</v>
+        <v>-598.042632171021</v>
       </c>
       <c r="D94">
-        <v>383.8031094229638</v>
+        <v>379.625367828979</v>
       </c>
       <c r="E94">
-        <v>870.992</v>
+        <v>883.068</v>
       </c>
       <c r="F94">
-        <v>1110.992</v>
+        <v>1123.068</v>
       </c>
       <c r="G94">
         <v>145.4</v>
@@ -9001,37 +9001,37 @@
         <v>144.5</v>
       </c>
       <c r="M94">
-        <v>163.0936256</v>
+        <v>164.8663824</v>
       </c>
       <c r="N94">
-        <v>-18.5936256</v>
+        <v>-20.36638240000002</v>
       </c>
       <c r="O94">
-        <v>-4.462470143999999</v>
+        <v>-4.887931776000005</v>
       </c>
       <c r="P94">
-        <v>-14.131155456</v>
+        <v>-15.47845062400001</v>
       </c>
       <c r="Q94">
-        <v>19.06884454399999</v>
+        <v>17.72154937599997</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3904920677860541</v>
+        <v>0.4397337917554905</v>
       </c>
       <c r="T94">
-        <v>5.812003454945867</v>
+        <v>6.642289662795278</v>
       </c>
       <c r="U94">
         <v>0.1468</v>
       </c>
       <c r="V94">
-        <v>0.2126385986724916</v>
+        <v>0.2103521621276261</v>
       </c>
       <c r="W94">
-        <v>0.1155846537148782</v>
+        <v>0.1159203025996645</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.8859941611353817</v>
+        <v>0.8764673421984419</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1385872468405723</v>
+        <v>0.1395972468405723</v>
       </c>
       <c r="C95">
-        <v>-598.042632171021</v>
+        <v>-614.2064027018446</v>
       </c>
       <c r="D95">
-        <v>379.625367828979</v>
+        <v>375.5375972981554</v>
       </c>
       <c r="E95">
-        <v>883.068</v>
+        <v>895.144</v>
       </c>
       <c r="F95">
-        <v>1123.068</v>
+        <v>1135.144</v>
       </c>
       <c r="G95">
         <v>145.4</v>
@@ -9083,37 +9083,37 @@
         <v>144.5</v>
       </c>
       <c r="M95">
-        <v>164.8663824</v>
+        <v>166.6391392</v>
       </c>
       <c r="N95">
-        <v>-20.36638240000002</v>
+        <v>-22.13913920000002</v>
       </c>
       <c r="O95">
-        <v>-4.887931776000005</v>
+        <v>-5.313393408000004</v>
       </c>
       <c r="P95">
-        <v>-15.47845062400001</v>
+        <v>-16.82574579200001</v>
       </c>
       <c r="Q95">
-        <v>17.72154937599997</v>
+        <v>16.37425420799998</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4397337917554905</v>
+        <v>0.5053894237147389</v>
       </c>
       <c r="T95">
-        <v>6.642289662795278</v>
+        <v>7.749337939927826</v>
       </c>
       <c r="U95">
         <v>0.1468</v>
       </c>
       <c r="V95">
-        <v>0.2103521621276261</v>
+        <v>0.2081143731688215</v>
       </c>
       <c r="W95">
-        <v>0.1159203025996645</v>
+        <v>0.116248810018817</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.8764673421984419</v>
+        <v>0.8671432215367564</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1395972468405723</v>
+        <v>0.1406072468405723</v>
       </c>
       <c r="C96">
-        <v>-614.2064027018446</v>
+        <v>-630.2830776070969</v>
       </c>
       <c r="D96">
-        <v>375.5375972981554</v>
+        <v>371.5369223929032</v>
       </c>
       <c r="E96">
-        <v>895.144</v>
+        <v>907.22</v>
       </c>
       <c r="F96">
-        <v>1135.144</v>
+        <v>1147.22</v>
       </c>
       <c r="G96">
         <v>145.4</v>
@@ -9165,37 +9165,37 @@
         <v>144.5</v>
       </c>
       <c r="M96">
-        <v>166.6391392</v>
+        <v>168.411896</v>
       </c>
       <c r="N96">
-        <v>-22.13913920000002</v>
+        <v>-23.91189600000001</v>
       </c>
       <c r="O96">
-        <v>-5.313393408000004</v>
+        <v>-5.738855040000002</v>
       </c>
       <c r="P96">
-        <v>-16.82574579200001</v>
+        <v>-18.17304096000001</v>
       </c>
       <c r="Q96">
-        <v>16.37425420799998</v>
+        <v>15.02695903999998</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.5053894237147389</v>
+        <v>0.597307308457687</v>
       </c>
       <c r="T96">
-        <v>7.749337939927826</v>
+        <v>9.299205527913395</v>
       </c>
       <c r="U96">
         <v>0.1468</v>
       </c>
       <c r="V96">
-        <v>0.2081143731688215</v>
+        <v>0.2059236955565182</v>
       </c>
       <c r="W96">
-        <v>0.116248810018817</v>
+        <v>0.1165704014923031</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.8671432215367564</v>
+        <v>0.858015398152159</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1406072468405723</v>
+        <v>0.1416172468405723</v>
       </c>
       <c r="C97">
-        <v>-630.2830776070969</v>
+        <v>-646.2754110855698</v>
       </c>
       <c r="D97">
-        <v>371.5369223929032</v>
+        <v>367.6205889144302</v>
       </c>
       <c r="E97">
-        <v>907.22</v>
+        <v>919.296</v>
       </c>
       <c r="F97">
-        <v>1147.22</v>
+        <v>1159.296</v>
       </c>
       <c r="G97">
         <v>145.4</v>
@@ -9247,37 +9247,37 @@
         <v>144.5</v>
       </c>
       <c r="M97">
-        <v>168.411896</v>
+        <v>170.1846528</v>
       </c>
       <c r="N97">
-        <v>-23.91189600000001</v>
+        <v>-25.68465280000001</v>
       </c>
       <c r="O97">
-        <v>-5.738855040000002</v>
+        <v>-6.164316672000002</v>
       </c>
       <c r="P97">
-        <v>-18.17304096000001</v>
+        <v>-19.52033612800001</v>
       </c>
       <c r="Q97">
-        <v>15.02695903999998</v>
+        <v>13.67966387199998</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.597307308457687</v>
+        <v>0.735184135572109</v>
       </c>
       <c r="T97">
-        <v>9.299205527913395</v>
+        <v>11.62400690989175</v>
       </c>
       <c r="U97">
         <v>0.1468</v>
       </c>
       <c r="V97">
-        <v>0.2059236955565182</v>
+        <v>0.2037786570611378</v>
       </c>
       <c r="W97">
-        <v>0.1165704014923031</v>
+        <v>0.116885293143425</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.858015398152159</v>
+        <v>0.8490777377547407</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1416172468405723</v>
+        <v>0.1426272468405723</v>
       </c>
       <c r="C98">
-        <v>-646.2754110855695</v>
+        <v>-662.1860424204345</v>
       </c>
       <c r="D98">
-        <v>367.6205889144302</v>
+        <v>363.7859575795653</v>
       </c>
       <c r="E98">
-        <v>919.2959999999998</v>
+        <v>931.3719999999998</v>
       </c>
       <c r="F98">
-        <v>1159.296</v>
+        <v>1171.372</v>
       </c>
       <c r="G98">
         <v>145.4</v>
@@ -9329,37 +9329,37 @@
         <v>144.5</v>
       </c>
       <c r="M98">
-        <v>170.1846528</v>
+        <v>171.9574096</v>
       </c>
       <c r="N98">
-        <v>-25.68465279999998</v>
+        <v>-27.45740960000001</v>
       </c>
       <c r="O98">
-        <v>-6.164316671999996</v>
+        <v>-6.589778304000001</v>
       </c>
       <c r="P98">
-        <v>-19.52033612799999</v>
+        <v>-20.86763129600001</v>
       </c>
       <c r="Q98">
-        <v>13.679663872</v>
+        <v>12.33236870399998</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.7351841355721073</v>
+        <v>0.9649788474294764</v>
       </c>
       <c r="T98">
-        <v>11.62400690989172</v>
+        <v>15.49867587985563</v>
       </c>
       <c r="U98">
         <v>0.1468</v>
       </c>
       <c r="V98">
-        <v>0.2037786570611378</v>
+        <v>0.2016778461636003</v>
       </c>
       <c r="W98">
-        <v>0.116885293143425</v>
+        <v>0.1171936921831835</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.8490777377547408</v>
+        <v>0.8403243590150011</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1426272468405723</v>
+        <v>0.1436372468405723</v>
       </c>
       <c r="C99">
-        <v>-662.1860424204345</v>
+        <v>-678.0175019107664</v>
       </c>
       <c r="D99">
-        <v>363.7859575795653</v>
+        <v>360.0304980892334</v>
       </c>
       <c r="E99">
-        <v>931.3719999999998</v>
+        <v>943.4479999999999</v>
       </c>
       <c r="F99">
-        <v>1171.372</v>
+        <v>1183.448</v>
       </c>
       <c r="G99">
         <v>145.4</v>
@@ -9411,37 +9411,37 @@
         <v>144.5</v>
       </c>
       <c r="M99">
-        <v>171.9574096</v>
+        <v>173.7301664</v>
       </c>
       <c r="N99">
-        <v>-27.45740960000001</v>
+        <v>-29.2301664</v>
       </c>
       <c r="O99">
-        <v>-6.589778304000001</v>
+        <v>-7.015239936</v>
       </c>
       <c r="P99">
-        <v>-20.86763129600001</v>
+        <v>-22.214926464</v>
       </c>
       <c r="Q99">
-        <v>12.33236870399998</v>
+        <v>10.98507353599999</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.9649788474294764</v>
+        <v>1.424568271144215</v>
       </c>
       <c r="T99">
-        <v>15.49867587985563</v>
+        <v>23.24801381978344</v>
       </c>
       <c r="U99">
         <v>0.1468</v>
       </c>
       <c r="V99">
-        <v>0.2016778461636003</v>
+        <v>0.1996199089578492</v>
       </c>
       <c r="W99">
-        <v>0.1171936921831835</v>
+        <v>0.1174957973649877</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.8403243590150011</v>
+        <v>0.8317496206577052</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1436372468405723</v>
+        <v>0.1446472468405723</v>
       </c>
       <c r="C100">
-        <v>-678.0175019107664</v>
+        <v>-693.7722164394232</v>
       </c>
       <c r="D100">
-        <v>360.0304980892334</v>
+        <v>356.3517835605767</v>
       </c>
       <c r="E100">
-        <v>943.4479999999999</v>
+        <v>955.5239999999999</v>
       </c>
       <c r="F100">
-        <v>1183.448</v>
+        <v>1195.524</v>
       </c>
       <c r="G100">
         <v>145.4</v>
@@ -9493,37 +9493,37 @@
         <v>144.5</v>
       </c>
       <c r="M100">
-        <v>173.7301664</v>
+        <v>175.5029232</v>
       </c>
       <c r="N100">
-        <v>-29.2301664</v>
+        <v>-31.0029232</v>
       </c>
       <c r="O100">
-        <v>-7.015239936</v>
+        <v>-7.440701567999999</v>
       </c>
       <c r="P100">
-        <v>-22.214926464</v>
+        <v>-23.562221632</v>
       </c>
       <c r="Q100">
-        <v>10.98507353599999</v>
+        <v>9.637778367999989</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.424568271144215</v>
+        <v>2.80333654228843</v>
       </c>
       <c r="T100">
-        <v>23.24801381978344</v>
+        <v>46.49602763956688</v>
       </c>
       <c r="U100">
         <v>0.1468</v>
       </c>
       <c r="V100">
-        <v>0.1996199089578492</v>
+        <v>0.1976035462411033</v>
       </c>
       <c r="W100">
-        <v>0.1174957973649877</v>
+        <v>0.1177917994118061</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.8317496206577052</v>
+        <v>0.8233481093379305</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1446472468405723</v>
-      </c>
-      <c r="C101">
-        <v>-693.7722164394232</v>
-      </c>
-      <c r="D101">
-        <v>356.3517835605767</v>
-      </c>
-      <c r="E101">
-        <v>955.5239999999999</v>
-      </c>
-      <c r="F101">
-        <v>1195.524</v>
-      </c>
-      <c r="G101">
-        <v>145.4</v>
-      </c>
-      <c r="H101">
-        <v>967.6</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>177.7</v>
-      </c>
-      <c r="K101">
-        <v>33.19999999999999</v>
-      </c>
-      <c r="L101">
-        <v>144.5</v>
-      </c>
-      <c r="M101">
-        <v>175.5029232</v>
-      </c>
-      <c r="N101">
-        <v>-31.0029232</v>
-      </c>
-      <c r="O101">
-        <v>-7.440701567999999</v>
-      </c>
-      <c r="P101">
-        <v>-23.562221632</v>
-      </c>
-      <c r="Q101">
-        <v>9.637778367999989</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.80333654228843</v>
-      </c>
-      <c r="T101">
-        <v>46.49602763956688</v>
-      </c>
-      <c r="U101">
-        <v>0.1468</v>
-      </c>
-      <c r="V101">
-        <v>0.1976035462411033</v>
-      </c>
-      <c r="W101">
-        <v>0.1177917994118061</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Ca2/CC</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.8233481093379305</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
